--- a/output1/MTL_val_predictions.xlsx
+++ b/output1/MTL_val_predictions.xlsx
@@ -488,7 +488,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5496492385864258</v>
+        <v>0.4767398834228516</v>
       </c>
       <c r="F2" t="n">
         <v>22.84931507</v>
@@ -518,7 +518,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5241456627845764</v>
+        <v>0.4584689438343048</v>
       </c>
       <c r="F3" t="n">
         <v>68.54794520999999</v>
@@ -548,7 +548,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5956528186798096</v>
+        <v>0.6077396869659424</v>
       </c>
       <c r="F4" t="n">
         <v>18.57534247</v>
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5682576298713684</v>
+        <v>0.5445164442062378</v>
       </c>
       <c r="F5" t="n">
         <v>4.175342466</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0381745882332325</v>
+        <v>0.004264768213033676</v>
       </c>
       <c r="F6" t="n">
         <v>5.128767123</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.595732569694519</v>
+        <v>0.5725575685501099</v>
       </c>
       <c r="F7" t="n">
         <v>2.431211499</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4864941537380219</v>
+        <v>0.4587244689464569</v>
       </c>
       <c r="F8" t="n">
         <v>7.359342916</v>
@@ -698,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5600594878196716</v>
+        <v>0.5427680611610413</v>
       </c>
       <c r="F9" t="n">
         <v>38.57084189</v>
@@ -728,7 +728,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5102696418762207</v>
+        <v>0.4660815298557281</v>
       </c>
       <c r="F10" t="n">
         <v>63.27720739</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5443202257156372</v>
+        <v>0.4956004321575165</v>
       </c>
       <c r="F11" t="n">
         <v>10.87474333</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4559046924114227</v>
+        <v>0.4495327174663544</v>
       </c>
       <c r="F12" t="n">
         <v>19.74537988</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.571883499622345</v>
+        <v>0.6215502023696899</v>
       </c>
       <c r="F13" t="n">
         <v>21.9137577</v>
@@ -827,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.868421052631578</v>
+        <v>3.868421052631577</v>
       </c>
     </row>
     <row r="14">
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5746970176696777</v>
+        <v>0.5225714445114136</v>
       </c>
       <c r="F14" t="n">
         <v>12.09034908</v>
@@ -878,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8315774202346802</v>
+        <v>0.9412357211112976</v>
       </c>
       <c r="F15" t="n">
         <v>19.31827515</v>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5587666034698486</v>
+        <v>0.5292917490005493</v>
       </c>
       <c r="F16" t="n">
         <v>17.24845996</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4616965055465698</v>
+        <v>0.4493134319782257</v>
       </c>
       <c r="F17" t="n">
         <v>11.86036961</v>
@@ -968,7 +968,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5134275555610657</v>
+        <v>0.6037221550941467</v>
       </c>
       <c r="F18" t="n">
         <v>9.494866529999999</v>
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6065057516098022</v>
+        <v>0.6105730533599854</v>
       </c>
       <c r="F19" t="n">
         <v>53.15811088</v>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5023269653320312</v>
+        <v>0.4617139399051666</v>
       </c>
       <c r="F20" t="n">
         <v>6.53798768</v>
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5404929518699646</v>
+        <v>0.4850120842456818</v>
       </c>
       <c r="F21" t="n">
         <v>3.318275154</v>
@@ -1088,7 +1088,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4879486858844757</v>
+        <v>0.470810741186142</v>
       </c>
       <c r="F22" t="n">
         <v>22.86652977</v>
@@ -1118,7 +1118,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5610945224761963</v>
+        <v>0.6590420007705688</v>
       </c>
       <c r="F23" t="n">
         <v>32.75564682</v>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5443490147590637</v>
+        <v>0.527923047542572</v>
       </c>
       <c r="F24" t="n">
         <v>1.77412731</v>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4781963229179382</v>
+        <v>0.4792601764202118</v>
       </c>
       <c r="F25" t="n">
         <v>54.80082136</v>
@@ -1208,7 +1208,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.642438530921936</v>
+        <v>0.6218076348304749</v>
       </c>
       <c r="F26" t="n">
         <v>55.12936345</v>
@@ -1238,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5574960708618164</v>
+        <v>0.5048346519470215</v>
       </c>
       <c r="F27" t="n">
         <v>37.78234086</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6044043898582458</v>
+        <v>0.5583125948905945</v>
       </c>
       <c r="F28" t="n">
         <v>3.879452055</v>
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5438740253448486</v>
+        <v>0.5229339003562927</v>
       </c>
       <c r="F29" t="n">
         <v>3.649315068</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5278803110122681</v>
+        <v>0.5049182772636414</v>
       </c>
       <c r="F30" t="n">
         <v>25.79055441</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3640369474887848</v>
+        <v>0.4587273597717285</v>
       </c>
       <c r="F31" t="n">
         <v>17.11704312</v>
@@ -1388,7 +1388,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8165023326873779</v>
+        <v>0.7860153317451477</v>
       </c>
       <c r="F32" t="n">
         <v>32.59137577</v>
@@ -1418,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4668945372104645</v>
+        <v>0.4234839379787445</v>
       </c>
       <c r="F33" t="n">
         <v>1.905544148</v>
@@ -1448,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5657647848129272</v>
+        <v>0.4908029735088348</v>
       </c>
       <c r="F34" t="n">
         <v>21.74948665</v>
@@ -1478,7 +1478,7 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6474353671073914</v>
+        <v>0.5585181713104248</v>
       </c>
       <c r="F35" t="n">
         <v>31.54004107</v>
@@ -1508,7 +1508,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7242593765258789</v>
+        <v>0.7291261553764343</v>
       </c>
       <c r="F36" t="n">
         <v>20.862423</v>
@@ -1538,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1928695440292358</v>
+        <v>0.2748091220855713</v>
       </c>
       <c r="F37" t="n">
         <v>6.735112936</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5202534198760986</v>
+        <v>0.5086556673049927</v>
       </c>
       <c r="F38" t="n">
         <v>1.379876797</v>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8058199882507324</v>
+        <v>0.8477616906166077</v>
       </c>
       <c r="F39" t="n">
         <v>16.85420945</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5638296008110046</v>
+        <v>0.5848798155784607</v>
       </c>
       <c r="F40" t="n">
         <v>6.669404517</v>
@@ -1658,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6511908769607544</v>
+        <v>0.4463933110237122</v>
       </c>
       <c r="F41" t="n">
         <v>21.61806982</v>
@@ -1688,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6659306287765503</v>
+        <v>0.6411996483802795</v>
       </c>
       <c r="F42" t="n">
         <v>21.65092402</v>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.387573778629303</v>
+        <v>0.6055847406387329</v>
       </c>
       <c r="F43" t="n">
         <v>16.82135524</v>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7149059772491455</v>
+        <v>0.7374709248542786</v>
       </c>
       <c r="F44" t="n">
         <v>26.90759754</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3331875503063202</v>
+        <v>0.3661037683486938</v>
       </c>
       <c r="F45" t="n">
         <v>8.31211499</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4922103881835938</v>
+        <v>0.5061317682266235</v>
       </c>
       <c r="F46" t="n">
         <v>4.501026694</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5145822167396545</v>
+        <v>0.5310874581336975</v>
       </c>
       <c r="F47" t="n">
         <v>14.16016427</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4578612446784973</v>
+        <v>0.4684324562549591</v>
       </c>
       <c r="F48" t="n">
         <v>13.99589322</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1943062543869019</v>
+        <v>0.3035711646080017</v>
       </c>
       <c r="F49" t="n">
         <v>1.741273101</v>
@@ -1928,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0573166161775589</v>
+        <v>0.02182356268167496</v>
       </c>
       <c r="F50" t="n">
         <v>32.88706366</v>
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.04756885766983032</v>
+        <v>0.09605732560157776</v>
       </c>
       <c r="F51" t="n">
         <v>5.848049281</v>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2280387729406357</v>
+        <v>0.2719877958297729</v>
       </c>
       <c r="F52" t="n">
         <v>4.468172485</v>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6068071126937866</v>
+        <v>0.591179370880127</v>
       </c>
       <c r="F53" t="n">
         <v>12.97741273</v>
@@ -2048,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5508480668067932</v>
+        <v>0.5729430913925171</v>
       </c>
       <c r="F54" t="n">
         <v>11.07095926412615</v>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4563838839530945</v>
+        <v>0.4061427116394043</v>
       </c>
       <c r="F55" t="n">
         <v>12.05650459921156</v>
@@ -2108,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5845379233360291</v>
+        <v>0.5478312373161316</v>
       </c>
       <c r="F56" t="n">
         <v>18.88961892247044</v>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4798689186573029</v>
+        <v>0.4584614336490631</v>
       </c>
       <c r="F57" t="n">
         <v>4.336399474375821</v>
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4771000742912292</v>
+        <v>0.4383372962474823</v>
       </c>
       <c r="F58" t="n">
         <v>11.92509855453351</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5445642471313477</v>
+        <v>0.4880102276802063</v>
       </c>
       <c r="F59" t="n">
         <v>6.340341655716163</v>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4949607253074646</v>
+        <v>0.4604231715202332</v>
       </c>
       <c r="F60" t="n">
         <v>14.7503285151117</v>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.461020439863205</v>
+        <v>0.425611823797226</v>
       </c>
       <c r="F61" t="n">
         <v>3.350854139290407</v>
@@ -2288,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.7062736749649048</v>
+        <v>0.6774824261665344</v>
       </c>
       <c r="F62" t="n">
         <v>19.44809461235217</v>
@@ -2318,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6842919588088989</v>
+        <v>0.7151908278465271</v>
       </c>
       <c r="F63" t="n">
         <v>24.90144546649146</v>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5434998273849487</v>
+        <v>0.520762026309967</v>
       </c>
       <c r="F64" t="n">
         <v>20.69645203679369</v>
@@ -2378,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7242258191108704</v>
+        <v>0.7205574512481689</v>
       </c>
       <c r="F65" t="n">
         <v>30.35479632063075</v>
@@ -2408,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4890400171279907</v>
+        <v>0.4614325761795044</v>
       </c>
       <c r="F66" t="n">
         <v>19.64520367936925</v>
@@ -2438,7 +2438,7 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5784375071525574</v>
+        <v>0.5295708179473877</v>
       </c>
       <c r="F67" t="n">
         <v>15.93298291721419</v>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1665694415569305</v>
+        <v>0.2534096539020538</v>
       </c>
       <c r="F68" t="n">
         <v>22.1108829568789</v>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2307407110929489</v>
+        <v>0.238665297627449</v>
       </c>
       <c r="F69" t="n">
         <v>6.50513347022587</v>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.6893825531005859</v>
+        <v>0.719298243522644</v>
       </c>
       <c r="F70" t="n">
         <v>7.39219712525667</v>
@@ -2558,7 +2558,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9340903759002686</v>
+        <v>0.9550449848175049</v>
       </c>
       <c r="F71" t="n">
         <v>21.4209445585216</v>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1118263006210327</v>
+        <v>0.1430906057357788</v>
       </c>
       <c r="F72" t="n">
         <v>5.38809034907598</v>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.349088579416275</v>
+        <v>0.5547928214073181</v>
       </c>
       <c r="F73" t="n">
         <v>6.8993839835729</v>
@@ -2648,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5402637124061584</v>
+        <v>0.648557722568512</v>
       </c>
       <c r="F74" t="n">
         <v>16.8542094455852</v>
@@ -2678,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5037456154823303</v>
+        <v>0.4930602610111237</v>
       </c>
       <c r="F75" t="n">
         <v>12.4188911704312</v>
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4424867928028107</v>
+        <v>0.5710975527763367</v>
       </c>
       <c r="F76" t="n">
         <v>22.735112936345</v>
@@ -2738,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0.4369530975818634</v>
+        <v>0.6265228986740112</v>
       </c>
       <c r="F77" t="n">
         <v>19.3511293634497</v>
@@ -2768,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.384336918592453</v>
+        <v>0.4860006272792816</v>
       </c>
       <c r="F78" t="n">
         <v>18.8583162217659</v>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.5665566921234131</v>
+        <v>0.578947901725769</v>
       </c>
       <c r="F79" t="n">
         <v>21.5852156057495</v>
@@ -2828,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3067848682403564</v>
+        <v>0.4321802258491516</v>
       </c>
       <c r="F80" t="n">
         <v>11.2689938398357</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.3208506107330322</v>
+        <v>0.3032693862915039</v>
       </c>
       <c r="F81" t="n">
         <v>10.1848049281314</v>
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.5046837329864502</v>
+        <v>0.6563616991043091</v>
       </c>
       <c r="F82" t="n">
         <v>7.72073921971253</v>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1294860988855362</v>
+        <v>0.1787033975124359</v>
       </c>
       <c r="F83" t="n">
         <v>7.88501026694045</v>
@@ -2948,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.3097530901432037</v>
+        <v>0.2761160731315613</v>
       </c>
       <c r="F84" t="n">
         <v>9.26488706365503</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0.296485424041748</v>
+        <v>0.3528292775154114</v>
       </c>
       <c r="F85" t="n">
         <v>2.10266940451745</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2784629166126251</v>
+        <v>0.459106981754303</v>
       </c>
       <c r="F86" t="n">
         <v>5.05954825462012</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1615320295095444</v>
+        <v>0.2335203140974045</v>
       </c>
       <c r="F87" t="n">
         <v>13.2731006160164</v>
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2536884248256683</v>
+        <v>0.3165940642356873</v>
       </c>
       <c r="F88" t="n">
         <v>6.70225872689938</v>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0.4063204824924469</v>
+        <v>0.5453083515167236</v>
       </c>
       <c r="F89" t="n">
         <v>15.8357289527721</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9036039113998413</v>
+        <v>0.9208603501319885</v>
       </c>
       <c r="F90" t="n">
         <v>17.0841889117043</v>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1053041964769363</v>
+        <v>0.149128645658493</v>
       </c>
       <c r="F91" t="n">
         <v>15.605749486653</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0.41681107878685</v>
+        <v>0.5501503944396973</v>
       </c>
       <c r="F92" t="n">
         <v>22.5051334702259</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0.313315212726593</v>
+        <v>0.4470033049583435</v>
       </c>
       <c r="F93" t="n">
         <v>8.08213552361396</v>
@@ -3248,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0.5518064498901367</v>
+        <v>0.6490840911865234</v>
       </c>
       <c r="F94" t="n">
         <v>6.01232032854209</v>
@@ -3278,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>0.3767296373844147</v>
+        <v>0.4210159480571747</v>
       </c>
       <c r="F95" t="n">
         <v>18.5626283367556</v>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4009983539581299</v>
+        <v>0.5637713670730591</v>
       </c>
       <c r="F96" t="n">
         <v>21.1909650924025</v>
@@ -3338,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>0.5436506867408752</v>
+        <v>0.5540193915367126</v>
       </c>
       <c r="F97" t="n">
         <v>21.2566735112936</v>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0796172246336937</v>
+        <v>0.1432075053453445</v>
       </c>
       <c r="F98" t="n">
         <v>11.3675564681725</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1039273142814636</v>
+        <v>0.1430706083774567</v>
       </c>
       <c r="F99" t="n">
         <v>4.63244353182752</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0.300694465637207</v>
+        <v>0.4197965860366821</v>
       </c>
       <c r="F100" t="n">
         <v>17.2813141683778</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0.2480542659759521</v>
+        <v>0.3854329884052277</v>
       </c>
       <c r="F101" t="n">
         <v>5.84804928131417</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0.2740929424762726</v>
+        <v>0.4176409840583801</v>
       </c>
       <c r="F102" t="n">
         <v>4.50102669404517</v>
@@ -3518,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8652356266975403</v>
+        <v>0.8795404434204102</v>
       </c>
       <c r="F103" t="n">
         <v>17.0184804928131</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0.1209423765540123</v>
+        <v>0.1735934317111969</v>
       </c>
       <c r="F104" t="n">
         <v>6.73511293634497</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1319385915994644</v>
+        <v>0.2215999066829681</v>
       </c>
       <c r="F105" t="n">
         <v>13.3388090349076</v>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7991034984588623</v>
+        <v>0.8622230887413025</v>
       </c>
       <c r="F106" t="n">
         <v>8.90349075975359</v>
@@ -3638,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>0.2379109859466553</v>
+        <v>0.3914904594421387</v>
       </c>
       <c r="F107" t="n">
         <v>17.2813141683778</v>
@@ -3668,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>0.371880054473877</v>
+        <v>0.4517839252948761</v>
       </c>
       <c r="F108" t="n">
         <v>1.01848049281314</v>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1752754002809525</v>
+        <v>0.2870405912399292</v>
       </c>
       <c r="F109" t="n">
         <v>4.99383983572895</v>
@@ -3728,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>0.6700995564460754</v>
+        <v>0.6358281373977661</v>
       </c>
       <c r="F110" t="n">
         <v>10.5462012320329</v>
@@ -3758,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5282894968986511</v>
+        <v>0.666100025177002</v>
       </c>
       <c r="F111" t="n">
         <v>20.0082135523614</v>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>0.3515690565109253</v>
+        <v>0.4246625900268555</v>
       </c>
       <c r="F112" t="n">
         <v>14.7515400410678</v>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>0.500673234462738</v>
+        <v>0.4475119411945343</v>
       </c>
       <c r="F113" t="n">
         <v>2.52977412731006</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>0.1295550763607025</v>
+        <v>0.2172129601240158</v>
       </c>
       <c r="F114" t="n">
         <v>4.17248459958932</v>
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.8864760994911194</v>
+        <v>0.8968354463577271</v>
       </c>
       <c r="F115" t="n">
         <v>20.7310061601643</v>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>0.2955207824707031</v>
+        <v>0.4572425186634064</v>
       </c>
       <c r="F116" t="n">
         <v>9.49486652977413</v>
@@ -3938,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.7577717900276184</v>
+        <v>0.7830641865730286</v>
       </c>
       <c r="F117" t="n">
         <v>24.1806981519507</v>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>0.2531856298446655</v>
+        <v>0.2211781293153763</v>
       </c>
       <c r="F118" t="n">
         <v>1.80698151950719</v>
@@ -3998,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3571160733699799</v>
+        <v>0.3255210220813751</v>
       </c>
       <c r="F119" t="n">
         <v>16.2299794661191</v>
@@ -4028,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3435958921909332</v>
+        <v>0.4798125624656677</v>
       </c>
       <c r="F120" t="n">
         <v>2.20123203285421</v>
@@ -4058,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0.2200252711772919</v>
+        <v>0.2917748093605042</v>
       </c>
       <c r="F121" t="n">
         <v>6.24229979466119</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2255107164382935</v>
+        <v>0.3297040462493896</v>
       </c>
       <c r="F122" t="n">
         <v>2.10266940451745</v>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2923441529273987</v>
+        <v>0.4101142585277557</v>
       </c>
       <c r="F123" t="n">
         <v>13.9958932238193</v>
@@ -4148,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0.8386633992195129</v>
+        <v>0.8489447236061096</v>
       </c>
       <c r="F124" t="n">
         <v>21.5852156057495</v>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>0.2758929431438446</v>
+        <v>0.2552494704723358</v>
       </c>
       <c r="F125" t="n">
         <v>2.10266940451745</v>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>0.3442427515983582</v>
+        <v>0.5144649147987366</v>
       </c>
       <c r="F126" t="n">
         <v>3.1211498973306</v>
@@ -4238,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>0.105985626578331</v>
+        <v>0.1330240964889526</v>
       </c>
       <c r="F127" t="n">
         <v>15.5400410677618</v>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>0.4287225306034088</v>
+        <v>0.3981083631515503</v>
       </c>
       <c r="F128" t="n">
         <v>69.99452055</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>0.3432368040084839</v>
+        <v>0.004560882691293955</v>
       </c>
       <c r="F129" t="n">
         <v>1.97260274</v>
@@ -4328,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0.5989916324615479</v>
+        <v>0.9584765434265137</v>
       </c>
       <c r="F130" t="n">
         <v>46.25753425</v>
@@ -4358,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>0.6573105454444885</v>
+        <v>0.9803722500801086</v>
       </c>
       <c r="F131" t="n">
         <v>61.84109589</v>
@@ -4388,7 +4388,7 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3634379208087921</v>
+        <v>0.3394227027893066</v>
       </c>
       <c r="F132" t="n">
         <v>8.219178082000001</v>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5798694491386414</v>
+        <v>0.7610005736351013</v>
       </c>
       <c r="F133" t="n">
         <v>2.95890411</v>
@@ -4448,7 +4448,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3823593854904175</v>
+        <v>0.03955287858843803</v>
       </c>
       <c r="F134" t="n">
         <v>28.20821918</v>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>0.4472517967224121</v>
+        <v>0.3752122521400452</v>
       </c>
       <c r="F135" t="n">
         <v>25.31506849</v>
@@ -4508,7 +4508,7 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>0.22087661921978</v>
+        <v>0.9970117807388306</v>
       </c>
       <c r="F136" t="n">
         <v>45.53593429</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3584509789943695</v>
+        <v>0.1266988962888718</v>
       </c>
       <c r="F137" t="n">
         <v>50.85831622</v>
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>0.9553249478340149</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="F138" t="n">
         <v>38.80082136</v>
@@ -4598,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>0.5218265056610107</v>
+        <v>0.01819802634418011</v>
       </c>
       <c r="F139" t="n">
         <v>16.95277207</v>
@@ -4628,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4700899124145508</v>
+        <v>0.390021950006485</v>
       </c>
       <c r="F140" t="n">
         <v>16.78850103</v>
@@ -4658,7 +4658,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.5235123038291931</v>
+        <v>0.9997257590293884</v>
       </c>
       <c r="F141" t="n">
         <v>43.36755647</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4437692761421204</v>
+        <v>0.5889907479286194</v>
       </c>
       <c r="F142" t="n">
         <v>28.25462012</v>
@@ -4718,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>0.425260454416275</v>
+        <v>0.01709791086614132</v>
       </c>
       <c r="F143" t="n">
         <v>50.03696099</v>
@@ -4748,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3524838387966156</v>
+        <v>0.02509872429072857</v>
       </c>
       <c r="F144" t="n">
         <v>4.73100616</v>
@@ -4778,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3060352802276611</v>
+        <v>0.1475230753421783</v>
       </c>
       <c r="F145" t="n">
         <v>40.01642711</v>
@@ -4808,7 +4808,7 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>0.4449941217899323</v>
+        <v>0.433978408575058</v>
       </c>
       <c r="F146" t="n">
         <v>57.3963039</v>
@@ -4838,7 +4838,7 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.6296622157096863</v>
+        <v>0.6277024745941162</v>
       </c>
       <c r="F147" t="n">
         <v>37.81519507</v>
@@ -4868,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>0.5407009720802307</v>
+        <v>0.3275613486766815</v>
       </c>
       <c r="F148" t="n">
         <v>4.73100616</v>
@@ -4898,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0.6081171631813049</v>
+        <v>0.9276244640350342</v>
       </c>
       <c r="F149" t="n">
         <v>26.80903491</v>
@@ -4928,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>0.2732712924480438</v>
+        <v>0.1217760294675827</v>
       </c>
       <c r="F150" t="n">
         <v>55.68788501</v>
@@ -4958,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>0.1379420161247253</v>
+        <v>0.3837695419788361</v>
       </c>
       <c r="F151" t="n">
         <v>12.48459959</v>
@@ -4988,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>0.6601576805114746</v>
+        <v>0.769121527671814</v>
       </c>
       <c r="F152" t="n">
         <v>22.01232033</v>
@@ -5018,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>0.4408259391784668</v>
+        <v>0.5976226329803467</v>
       </c>
       <c r="F153" t="n">
         <v>63.27720739</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>0.577195405960083</v>
+        <v>0.9973115921020508</v>
       </c>
       <c r="F154" t="n">
         <v>15.21149897</v>
@@ -5078,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>0.401328057050705</v>
+        <v>0.008705609478056431</v>
       </c>
       <c r="F155" t="n">
         <v>31.82465753</v>
@@ -5108,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>0.06264141947031021</v>
+        <v>0.0536351352930069</v>
       </c>
       <c r="F156" t="n">
         <v>9.297741273</v>
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>0.3363555073738098</v>
+        <v>0.3617024123668671</v>
       </c>
       <c r="F157" t="n">
         <v>5.420944559</v>
@@ -5168,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>0.7932395339012146</v>
+        <v>0.7059441208839417</v>
       </c>
       <c r="F158" t="n">
         <v>19.38398357</v>
@@ -5198,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>0.2921304702758789</v>
+        <v>0.2834256589412689</v>
       </c>
       <c r="F159" t="n">
         <v>6.110882957</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>0.8411197066307068</v>
+        <v>0.001062016934156418</v>
       </c>
       <c r="F160" t="n">
         <v>11.53182752</v>
@@ -5258,7 +5258,7 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0.6309002637863159</v>
+        <v>0.7541452646255493</v>
       </c>
       <c r="F161" t="n">
         <v>28.74743326</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>0.5491147041320801</v>
+        <v>0.4202691614627838</v>
       </c>
       <c r="F162" t="n">
         <v>4.895277207</v>
@@ -5318,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>0.3901675343513489</v>
+        <v>0.4529158174991608</v>
       </c>
       <c r="F163" t="n">
         <v>22.50513347</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>0.4445759356021881</v>
+        <v>0.3563429415225983</v>
       </c>
       <c r="F164" t="n">
         <v>2.858316222</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>0.9280622601509094</v>
+        <v>0.9999284744262695</v>
       </c>
       <c r="F165" t="n">
         <v>6.603696099</v>
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>0.5047138929367065</v>
+        <v>0.03590721264481544</v>
       </c>
       <c r="F166" t="n">
         <v>5.683778234</v>
@@ -5438,7 +5438,7 @@
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>0.6482212543487549</v>
+        <v>0.6683385968208313</v>
       </c>
       <c r="F167" t="n">
         <v>4.271047228</v>
@@ -5468,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>0.6183497309684753</v>
+        <v>0.5056533217430115</v>
       </c>
       <c r="F168" t="n">
         <v>20.27104723</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>0.3864043056964874</v>
+        <v>0.1474146395921707</v>
       </c>
       <c r="F169" t="n">
         <v>5.486652977</v>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>0.8016430139541626</v>
+        <v>0.8076453804969788</v>
       </c>
       <c r="F170" t="n">
         <v>12.8788501</v>
@@ -5558,7 +5558,7 @@
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>0.8500332832336426</v>
+        <v>0.8509766459465027</v>
       </c>
       <c r="F171" t="n">
         <v>36.00821355</v>
@@ -5588,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>0.8811150193214417</v>
+        <v>0.6892842054367065</v>
       </c>
       <c r="F172" t="n">
         <v>55.16221766</v>
@@ -5618,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7515200972557068</v>
+        <v>0.4743725061416626</v>
       </c>
       <c r="F173" t="n">
         <v>55.55646817</v>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>0.07229314744472504</v>
+        <v>0.1494805812835693</v>
       </c>
       <c r="F174" t="n">
         <v>30.29158111</v>
@@ -5678,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>0.5363423228263855</v>
+        <v>0.3727218508720398</v>
       </c>
       <c r="F175" t="n">
         <v>54.73511294</v>
@@ -5708,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>0.8579208850860596</v>
+        <v>0.9181332588195801</v>
       </c>
       <c r="F176" t="n">
         <v>4.008213552</v>
@@ -5738,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>0.3477881848812103</v>
+        <v>0.1708170920610428</v>
       </c>
       <c r="F177" t="n">
         <v>32.42710472</v>
@@ -5768,7 +5768,7 @@
         <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>0.8652682900428772</v>
+        <v>0.7290658354759216</v>
       </c>
       <c r="F178" t="n">
         <v>43.59753593</v>
@@ -5798,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>0.6899327039718628</v>
+        <v>0.7774497866630554</v>
       </c>
       <c r="F179" t="n">
         <v>29.99589322</v>
@@ -5828,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>0.4371689558029175</v>
+        <v>0.743639349937439</v>
       </c>
       <c r="F180" t="n">
         <v>2.825229960578187</v>
@@ -5858,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>0.5071523785591125</v>
+        <v>0.5327600836753845</v>
       </c>
       <c r="F181" t="n">
         <v>3.219448094612352</v>
@@ -5888,7 +5888,7 @@
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>0.7080786824226379</v>
+        <v>0.9758054614067078</v>
       </c>
       <c r="F182" t="n">
         <v>17.96977660972405</v>
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>0.5893372893333435</v>
+        <v>0.9862128496170044</v>
       </c>
       <c r="F183" t="n">
         <v>7.030223390275952</v>
@@ -5948,7 +5948,7 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0.5320782065391541</v>
+        <v>0.9872509241104126</v>
       </c>
       <c r="F184" t="n">
         <v>15.70302233902759</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>0.4132170081138611</v>
+        <v>0.2678764760494232</v>
       </c>
       <c r="F185" t="n">
         <v>23.42312746386333</v>
@@ -6008,7 +6008,7 @@
         <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>0.341940701007843</v>
+        <v>0.06587643921375275</v>
       </c>
       <c r="F186" t="n">
         <v>12.87779237844941</v>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>0.33208829164505</v>
+        <v>0.5463776588439941</v>
       </c>
       <c r="F187" t="n">
         <v>29.86202365308804</v>
@@ -6068,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="E188" t="n">
-        <v>0.8408506512641907</v>
+        <v>0.9945425987243652</v>
       </c>
       <c r="F188" t="n">
         <v>34.13272010512483</v>
@@ -6098,7 +6098,7 @@
         <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2671933174133301</v>
+        <v>5.029831663705409e-05</v>
       </c>
       <c r="F189" t="n">
         <v>13.00919842312746</v>
@@ -6128,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>0.7813859581947327</v>
+        <v>0.9001011848449707</v>
       </c>
       <c r="F190" t="n">
         <v>9.789750328515112</v>
@@ -6158,7 +6158,7 @@
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>0.5387683510780334</v>
+        <v>0.8110839128494263</v>
       </c>
       <c r="F191" t="n">
         <v>32.75295663600525</v>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>0.7707893848419189</v>
+        <v>0.9794868230819702</v>
       </c>
       <c r="F192" t="n">
         <v>19.84231274638633</v>
@@ -6218,7 +6218,7 @@
         <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>0.2544268071651459</v>
+        <v>1.09151460492285e-05</v>
       </c>
       <c r="F193" t="n">
         <v>14.32325886990802</v>
@@ -6248,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>0.9222375154495239</v>
+        <v>0.7779423594474792</v>
       </c>
       <c r="F194" t="n">
         <v>15.6386036960986</v>
@@ -6278,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0.5536589622497559</v>
+        <v>0.7858719825744629</v>
       </c>
       <c r="F195" t="n">
         <v>20.0739219712526</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.6412834525108337</v>
+        <v>0.8117032647132874</v>
       </c>
       <c r="F196" t="n">
         <v>12.8459958932238</v>
@@ -6338,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>0.3588053286075592</v>
+        <v>0.0003315531939733773</v>
       </c>
       <c r="F197" t="n">
         <v>1.18275154004107</v>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>0.5062094926834106</v>
+        <v>0.0530087798833847</v>
       </c>
       <c r="F198" t="n">
         <v>2.62833675564682</v>
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="E199" t="n">
-        <v>0.6517367362976074</v>
+        <v>0.5926802754402161</v>
       </c>
       <c r="F199" t="n">
         <v>6.60369609856263</v>
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>0.7669953107833862</v>
+        <v>0.7920259237289429</v>
       </c>
       <c r="F200" t="n">
         <v>4.27104722792608</v>
@@ -6458,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="E201" t="n">
-        <v>0.3061873018741608</v>
+        <v>3.978890526923351e-05</v>
       </c>
       <c r="F201" t="n">
         <v>2.29979466119096</v>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3506491184234619</v>
+        <v>0.03099586628377438</v>
       </c>
       <c r="F202" t="n">
         <v>9.88911704312115</v>
@@ -6518,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>0.516970157623291</v>
+        <v>0.08559058606624603</v>
       </c>
       <c r="F203" t="n">
         <v>5.38809034907598</v>
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2858763933181763</v>
+        <v>0.2657818496227264</v>
       </c>
       <c r="F204" t="n">
         <v>5.51950718685832</v>
@@ -6578,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>0.8693191409111023</v>
+        <v>0.9422008395195007</v>
       </c>
       <c r="F205" t="n">
         <v>21.2566735112936</v>
@@ -6608,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2451710253953934</v>
+        <v>8.054701174842194e-05</v>
       </c>
       <c r="F206" t="n">
         <v>8.016427104722791</v>
@@ -6638,7 +6638,7 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>0.5503996610641479</v>
+        <v>0.4582481384277344</v>
       </c>
       <c r="F207" t="n">
         <v>20.6981519507187</v>
@@ -6668,7 +6668,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2432093620300293</v>
+        <v>0.005547075532376766</v>
       </c>
       <c r="F208" t="n">
         <v>5.38809034907598</v>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>0.2090697139501572</v>
+        <v>0.02377132326364517</v>
       </c>
       <c r="F209" t="n">
         <v>2.59548254620123</v>
@@ -6728,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>0.6052219271659851</v>
+        <v>0.8048470616340637</v>
       </c>
       <c r="F210" t="n">
         <v>20.5010266940452</v>
@@ -6758,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3401891887187958</v>
+        <v>0.6541805267333984</v>
       </c>
       <c r="F211" t="n">
         <v>19.1868583162218</v>
@@ -6788,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>0.2391880452632904</v>
+        <v>0.0002192862302763388</v>
       </c>
       <c r="F212" t="n">
         <v>3.5482546201232</v>
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="E213" t="n">
-        <v>0.6262534856796265</v>
+        <v>0.1083730235695839</v>
       </c>
       <c r="F213" t="n">
         <v>23.6878850102669</v>
@@ -6848,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>0.3191244900226593</v>
+        <v>0.06822821497917175</v>
       </c>
       <c r="F214" t="n">
         <v>15.6386036960986</v>
@@ -6878,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="E215" t="n">
-        <v>0.3330126106739044</v>
+        <v>0.005717364605516195</v>
       </c>
       <c r="F215" t="n">
         <v>8.706365503080081</v>
@@ -6908,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>0.1547476947307587</v>
+        <v>0.006123118102550507</v>
       </c>
       <c r="F216" t="n">
         <v>2.06981519507187</v>
@@ -6938,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>0.2627665996551514</v>
+        <v>0.09634247422218323</v>
       </c>
       <c r="F217" t="n">
         <v>2.13552361396304</v>
@@ -6968,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>0.3333288431167603</v>
+        <v>0.04456562548875809</v>
       </c>
       <c r="F218" t="n">
         <v>12.8459958932238</v>
@@ -6998,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>0.194032609462738</v>
+        <v>0.05541450530290604</v>
       </c>
       <c r="F219" t="n">
         <v>3.74537987679671</v>
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>0.2064983695745468</v>
+        <v>0.0267900787293911</v>
       </c>
       <c r="F220" t="n">
         <v>3.97535934291581</v>
@@ -7058,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>0.4157946109771729</v>
+        <v>0.4541604220867157</v>
       </c>
       <c r="F221" t="n">
         <v>19.2854209445585</v>
@@ -7088,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>0.4346817433834076</v>
+        <v>0.2927017211914062</v>
       </c>
       <c r="F222" t="n">
         <v>23.2279260780287</v>
@@ -7118,7 +7118,7 @@
         <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>0.4083020389080048</v>
+        <v>0.4401217997074127</v>
       </c>
       <c r="F223" t="n">
         <v>5.94661190965092</v>
@@ -7148,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="E224" t="n">
-        <v>0.632453441619873</v>
+        <v>0.6184821128845215</v>
       </c>
       <c r="F224" t="n">
         <v>19.2854209445585</v>
@@ -7178,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>0.4623185396194458</v>
+        <v>0.6116769313812256</v>
       </c>
       <c r="F225" t="n">
         <v>10.8418891170431</v>
@@ -7208,7 +7208,7 @@
         <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>0.3061751425266266</v>
+        <v>0.1784835010766983</v>
       </c>
       <c r="F226" t="n">
         <v>21.6509240246407</v>
@@ -7238,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="E227" t="n">
-        <v>0.4185311496257782</v>
+        <v>0.004484412726014853</v>
       </c>
       <c r="F227" t="n">
         <v>8.24640657084189</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>0.5208683013916016</v>
+        <v>0.6809523701667786</v>
       </c>
       <c r="F228" t="n">
         <v>2.13552361396304</v>
@@ -7298,7 +7298,7 @@
         <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>0.5645183920860291</v>
+        <v>0.8073741793632507</v>
       </c>
       <c r="F229" t="n">
         <v>20.5667351129363</v>
@@ -7328,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>0.6809287667274475</v>
+        <v>0.5839840173721313</v>
       </c>
       <c r="F230" t="n">
         <v>15.4414784394251</v>
@@ -7358,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>0.8001611828804016</v>
+        <v>0.9746379852294922</v>
       </c>
       <c r="F231" t="n">
         <v>2.10266940451745</v>
@@ -7388,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>0.3930656313896179</v>
+        <v>0.5040243268013</v>
       </c>
       <c r="F232" t="n">
         <v>5.65092402464066</v>
@@ -7418,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>0.356369286775589</v>
+        <v>0.04313918203115463</v>
       </c>
       <c r="F233" t="n">
         <v>3.5482546201232</v>
@@ -7448,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="E234" t="n">
-        <v>0.5499564409255981</v>
+        <v>0.8127700090408325</v>
       </c>
       <c r="F234" t="n">
         <v>2.62833675564682</v>
@@ -7478,7 +7478,7 @@
         <v>1</v>
       </c>
       <c r="E235" t="n">
-        <v>0.2760604619979858</v>
+        <v>0.07549934089183807</v>
       </c>
       <c r="F235" t="n">
         <v>11.4004106776181</v>
@@ -7508,7 +7508,7 @@
         <v>1</v>
       </c>
       <c r="E236" t="n">
-        <v>0.2482780069112778</v>
+        <v>0.00730642257258296</v>
       </c>
       <c r="F236" t="n">
         <v>22.4065708418891</v>
@@ -7538,7 +7538,7 @@
         <v>1</v>
       </c>
       <c r="E237" t="n">
-        <v>0.6706086993217468</v>
+        <v>0.8515880107879639</v>
       </c>
       <c r="F237" t="n">
         <v>20.0739219712526</v>
@@ -7568,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="E238" t="n">
-        <v>0.6464133262634277</v>
+        <v>0.4961467981338501</v>
       </c>
       <c r="F238" t="n">
         <v>12.8459958932238</v>
@@ -7598,7 +7598,7 @@
         <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>0.5421270132064819</v>
+        <v>0.6202610731124878</v>
       </c>
       <c r="F239" t="n">
         <v>20.7310061601643</v>
@@ -7628,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="E240" t="n">
-        <v>0.2240624278783798</v>
+        <v>0.3224597573280334</v>
       </c>
       <c r="F240" t="n">
         <v>1.93839835728953</v>
@@ -7658,7 +7658,7 @@
         <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>0.1778600066900253</v>
+        <v>0.001249926630407572</v>
       </c>
       <c r="F241" t="n">
         <v>1.70841889117043</v>
@@ -7688,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0.5911886096000671</v>
+        <v>0.8846017122268677</v>
       </c>
       <c r="F242" t="n">
         <v>20.0082135523614</v>
@@ -7718,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="E243" t="n">
-        <v>0.8032696843147278</v>
+        <v>0.7484160661697388</v>
       </c>
       <c r="F243" t="n">
         <v>0.197125256673511</v>
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="E244" t="n">
-        <v>0.1883243024349213</v>
+        <v>0.03951836749911308</v>
       </c>
       <c r="F244" t="n">
         <v>15.8028747433265</v>
@@ -7778,7 +7778,7 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0.7710797786712646</v>
+        <v>0.8753542304039001</v>
       </c>
       <c r="F245" t="n">
         <v>21.0595482546201</v>
@@ -7808,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="E246" t="n">
-        <v>0.3965602219104767</v>
+        <v>0.1293750703334808</v>
       </c>
       <c r="F246" t="n">
         <v>2.16837782340862</v>
@@ -7838,7 +7838,7 @@
         <v>0</v>
       </c>
       <c r="E247" t="n">
-        <v>0.2582205832004547</v>
+        <v>0.001224590698257089</v>
       </c>
       <c r="F247" t="n">
         <v>0.8542094455852161</v>
@@ -7868,7 +7868,7 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>0.4010169208049774</v>
+        <v>0.4918453991413116</v>
       </c>
       <c r="F248" t="n">
         <v>18.8911704312115</v>
@@ -7898,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="E249" t="n">
-        <v>0.4367163181304932</v>
+        <v>0.7068896889686584</v>
       </c>
       <c r="F249" t="n">
         <v>18.6611909650924</v>
@@ -7928,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="n">
-        <v>0.1864264756441116</v>
+        <v>0.04546045884490013</v>
       </c>
       <c r="F250" t="n">
         <v>3.21971252566735</v>
@@ -7958,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="E251" t="n">
-        <v>0.3958486914634705</v>
+        <v>0.03439145162701607</v>
       </c>
       <c r="F251" t="n">
         <v>10.1190965092402</v>
@@ -7988,7 +7988,7 @@
         <v>0</v>
       </c>
       <c r="E252" t="n">
-        <v>0.4437598884105682</v>
+        <v>0.8292739987373352</v>
       </c>
       <c r="F252" t="n">
         <v>10.3490759753593</v>
@@ -8018,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="E253" t="n">
-        <v>0.4980023205280304</v>
+        <v>0.7346124649047852</v>
       </c>
       <c r="F253" t="n">
         <v>20.5667351129363</v>
@@ -8048,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0.6045128107070923</v>
+        <v>0.5625779628753662</v>
       </c>
       <c r="F254" t="n">
         <v>15.87945205</v>
@@ -8078,7 +8078,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="n">
-        <v>0.891018807888031</v>
+        <v>0.6997205018997192</v>
       </c>
       <c r="F255" t="n">
         <v>7.956164384</v>
@@ -8108,7 +8108,7 @@
         <v>0</v>
       </c>
       <c r="E256" t="n">
-        <v>0.000276048929663375</v>
+        <v>0.0005274246213957667</v>
       </c>
       <c r="F256" t="n">
         <v>4.536986301</v>
@@ -8138,7 +8138,7 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5971081852912903</v>
+        <v>0.6257792115211487</v>
       </c>
       <c r="F257" t="n">
         <v>36.5260274</v>
@@ -8168,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0.2723463773727417</v>
+        <v>0.3612602949142456</v>
       </c>
       <c r="F258" t="n">
         <v>39.15616438</v>
@@ -8198,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0.3576207756996155</v>
+        <v>0.5290019512176514</v>
       </c>
       <c r="F259" t="n">
         <v>51.67967146</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="E260" t="n">
-        <v>0.2553677260875702</v>
+        <v>0.3854657709598541</v>
       </c>
       <c r="F260" t="n">
         <v>43.33470226</v>
@@ -8258,7 +8258,7 @@
         <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9738849997520447</v>
+        <v>0.8044655323028564</v>
       </c>
       <c r="F261" t="n">
         <v>21.2238193</v>
@@ -8288,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="E262" t="n">
-        <v>0.4104906916618347</v>
+        <v>0.424596756696701</v>
       </c>
       <c r="F262" t="n">
         <v>7.195071869</v>
@@ -8318,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="E263" t="n">
-        <v>0.8249602913856506</v>
+        <v>0.5204548835754395</v>
       </c>
       <c r="F263" t="n">
         <v>47.21149897</v>
@@ -8348,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="E264" t="n">
-        <v>0.3325500190258026</v>
+        <v>0.4450851082801819</v>
       </c>
       <c r="F264" t="n">
         <v>5.256673511</v>
@@ -8378,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="E265" t="n">
-        <v>0.4383500218391418</v>
+        <v>0.4646996855735779</v>
       </c>
       <c r="F265" t="n">
         <v>32.6899384</v>
@@ -8408,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="E266" t="n">
-        <v>0.3538788259029388</v>
+        <v>0.5884209275245667</v>
       </c>
       <c r="F266" t="n">
         <v>16.03285421</v>
@@ -8438,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.568915069103241</v>
+        <v>0.6710522174835205</v>
       </c>
       <c r="F267" t="n">
         <v>25.98767967</v>
@@ -8468,7 +8468,7 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0.5633047223091125</v>
+        <v>0.6374096274375916</v>
       </c>
       <c r="F268" t="n">
         <v>47.70431212</v>
@@ -8498,7 +8498,7 @@
         <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0.8596478700637817</v>
+        <v>0.6703795194625854</v>
       </c>
       <c r="F269" t="n">
         <v>55.35934292</v>
@@ -8528,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>0.4467136263847351</v>
+        <v>0.5222286581993103</v>
       </c>
       <c r="F270" t="n">
         <v>31.17864476</v>
@@ -8558,7 +8558,7 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0.454803466796875</v>
+        <v>0.4535682201385498</v>
       </c>
       <c r="F271" t="n">
         <v>41.56057495</v>
@@ -8588,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0004208599275443703</v>
+        <v>0.004126217216253281</v>
       </c>
       <c r="F272" t="n">
         <v>12.8788501</v>
@@ -8618,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="E273" t="n">
-        <v>0.1470234394073486</v>
+        <v>0.3287971019744873</v>
       </c>
       <c r="F273" t="n">
         <v>9.724845996000001</v>
@@ -8648,7 +8648,7 @@
         <v>1</v>
       </c>
       <c r="E274" t="n">
-        <v>0.2741762697696686</v>
+        <v>0.3789379298686981</v>
       </c>
       <c r="F274" t="n">
         <v>22.11088296</v>
@@ -8678,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="E275" t="n">
-        <v>0.3412385284900665</v>
+        <v>0.4509744942188263</v>
       </c>
       <c r="F275" t="n">
         <v>3.58110883</v>
@@ -8708,7 +8708,7 @@
         <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>0.1490191966295242</v>
+        <v>0.305987685918808</v>
       </c>
       <c r="F276" t="n">
         <v>53.51950719</v>
@@ -8738,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="E277" t="n">
-        <v>0.3613285720348358</v>
+        <v>0.488302081823349</v>
       </c>
       <c r="F277" t="n">
         <v>13.33880904</v>
@@ -8768,7 +8768,7 @@
         <v>1</v>
       </c>
       <c r="E278" t="n">
-        <v>0.3094297349452972</v>
+        <v>0.4331047236919403</v>
       </c>
       <c r="F278" t="n">
         <v>28.60273973</v>
@@ -8798,7 +8798,7 @@
         <v>1</v>
       </c>
       <c r="E279" t="n">
-        <v>0.2396535128355026</v>
+        <v>0.4578507542610168</v>
       </c>
       <c r="F279" t="n">
         <v>32.28493151</v>
@@ -8828,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="E280" t="n">
-        <v>0.1932410150766373</v>
+        <v>0.4914396703243256</v>
       </c>
       <c r="F280" t="n">
         <v>19.13424658</v>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
       <c r="E281" t="n">
-        <v>0.6024755239486694</v>
+        <v>0.6075348854064941</v>
       </c>
       <c r="F281" t="n">
         <v>3.876796715</v>
@@ -8888,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="E282" t="n">
-        <v>0.5379584431648254</v>
+        <v>0.7017840147018433</v>
       </c>
       <c r="F282" t="n">
         <v>42.90759754</v>
@@ -8918,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="E283" t="n">
-        <v>0.7692936062812805</v>
+        <v>0.8137814402580261</v>
       </c>
       <c r="F283" t="n">
         <v>12.15605749</v>
@@ -8948,7 +8948,7 @@
         <v>1</v>
       </c>
       <c r="E284" t="n">
-        <v>0.5707618594169617</v>
+        <v>0.6040893197059631</v>
       </c>
       <c r="F284" t="n">
         <v>32.72279261</v>
@@ -8978,7 +8978,7 @@
         <v>1</v>
       </c>
       <c r="E285" t="n">
-        <v>0.3966613113880157</v>
+        <v>0.3771113753318787</v>
       </c>
       <c r="F285" t="n">
         <v>26.02053388</v>
@@ -9008,7 +9008,7 @@
         <v>1</v>
       </c>
       <c r="E286" t="n">
-        <v>0.426059901714325</v>
+        <v>0.5845267772674561</v>
       </c>
       <c r="F286" t="n">
         <v>16.32854209</v>
@@ -9038,7 +9038,7 @@
         <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>0.5200557112693787</v>
+        <v>0.4929423034191132</v>
       </c>
       <c r="F287" t="n">
         <v>15.60574949</v>
@@ -9068,7 +9068,7 @@
         <v>0</v>
       </c>
       <c r="E288" t="n">
-        <v>0.1913138628005981</v>
+        <v>0.0520358607172966</v>
       </c>
       <c r="F288" t="n">
         <v>9.264887064</v>
@@ -9098,7 +9098,7 @@
         <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>0.4516688585281372</v>
+        <v>0.4172084331512451</v>
       </c>
       <c r="F289" t="n">
         <v>20.46817248</v>
@@ -9128,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="E290" t="n">
-        <v>0.8183523416519165</v>
+        <v>0.7701674699783325</v>
       </c>
       <c r="F290" t="n">
         <v>17.83983573</v>
@@ -9158,7 +9158,7 @@
         <v>1</v>
       </c>
       <c r="E291" t="n">
-        <v>0.8605273962020874</v>
+        <v>0.8969286680221558</v>
       </c>
       <c r="F291" t="n">
         <v>22.53798768</v>
@@ -9188,7 +9188,7 @@
         <v>1</v>
       </c>
       <c r="E292" t="n">
-        <v>0.3496920764446259</v>
+        <v>0.2874447107315063</v>
       </c>
       <c r="F292" t="n">
         <v>15.6386037</v>
@@ -9218,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="E293" t="n">
-        <v>0.3282868564128876</v>
+        <v>0.3414804041385651</v>
       </c>
       <c r="F293" t="n">
         <v>23.58932238</v>
@@ -9248,7 +9248,7 @@
         <v>1</v>
       </c>
       <c r="E294" t="n">
-        <v>0.06656692177057266</v>
+        <v>0.5069972276687622</v>
       </c>
       <c r="F294" t="n">
         <v>29.40451745</v>
@@ -9278,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="E295" t="n">
-        <v>0.01040445454418659</v>
+        <v>0.03527078777551651</v>
       </c>
       <c r="F295" t="n">
         <v>31.54004107</v>
@@ -9308,7 +9308,7 @@
         <v>0</v>
       </c>
       <c r="E296" t="n">
-        <v>0.03313590586185455</v>
+        <v>0.5427783131599426</v>
       </c>
       <c r="F296" t="n">
         <v>2.95687885</v>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="E297" t="n">
-        <v>0.4406371116638184</v>
+        <v>0.4310459792613983</v>
       </c>
       <c r="F297" t="n">
         <v>6.997946612</v>
@@ -9368,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="E298" t="n">
-        <v>0.2043032944202423</v>
+        <v>0.1361828446388245</v>
       </c>
       <c r="F298" t="n">
         <v>1.741273101</v>
@@ -9398,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="E299" t="n">
-        <v>0.4501887261867523</v>
+        <v>0.4113463461399078</v>
       </c>
       <c r="F299" t="n">
         <v>31.80287474</v>
@@ -9428,7 +9428,7 @@
         <v>0</v>
       </c>
       <c r="E300" t="n">
-        <v>0.1123528629541397</v>
+        <v>0.2805613577365875</v>
       </c>
       <c r="F300" t="n">
         <v>14.81724846</v>
@@ -9458,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="E301" t="n">
-        <v>2.775741165805812e-07</v>
+        <v>0.0008482512203045189</v>
       </c>
       <c r="F301" t="n">
         <v>15.37577002</v>
@@ -9488,7 +9488,7 @@
         <v>1</v>
       </c>
       <c r="E302" t="n">
-        <v>0.6387244462966919</v>
+        <v>0.6628818511962891</v>
       </c>
       <c r="F302" t="n">
         <v>33.7412731</v>
@@ -9518,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="E303" t="n">
-        <v>0.3189122378826141</v>
+        <v>0.3760225176811218</v>
       </c>
       <c r="F303" t="n">
         <v>30.78439425</v>
@@ -9548,7 +9548,7 @@
         <v>0</v>
       </c>
       <c r="E304" t="n">
-        <v>3.719527512657805e-06</v>
+        <v>0.0007788615766912699</v>
       </c>
       <c r="F304" t="n">
         <v>22.57084189</v>
@@ -9578,7 +9578,7 @@
         <v>0</v>
       </c>
       <c r="E305" t="n">
-        <v>0.4423544406890869</v>
+        <v>0.4374299347400665</v>
       </c>
       <c r="F305" t="n">
         <v>27.89322382</v>
@@ -9608,7 +9608,7 @@
         <v>1</v>
       </c>
       <c r="E306" t="n">
-        <v>0.5917978286743164</v>
+        <v>0.5361164808273315</v>
       </c>
       <c r="F306" t="n">
         <v>13.27201051248357</v>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="E307" t="n">
-        <v>0.7299164533615112</v>
+        <v>0.6188527941703796</v>
       </c>
       <c r="F307" t="n">
         <v>11.95795006570302</v>
@@ -9668,7 +9668,7 @@
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>0.9735939502716064</v>
+        <v>0.9719980955123901</v>
       </c>
       <c r="F308" t="n">
         <v>5.091984231274639</v>
@@ -9698,7 +9698,7 @@
         <v>0</v>
       </c>
       <c r="E309" t="n">
-        <v>0.4702019691467285</v>
+        <v>0.4440081119537354</v>
       </c>
       <c r="F309" t="n">
         <v>6.241787122207621</v>
@@ -9728,7 +9728,7 @@
         <v>0</v>
       </c>
       <c r="E310" t="n">
-        <v>0.08786991983652115</v>
+        <v>0.2453113496303558</v>
       </c>
       <c r="F310" t="n">
         <v>0.3942181340341655</v>
@@ -9758,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="E311" t="n">
-        <v>0.2024570107460022</v>
+        <v>0.3213271498680115</v>
       </c>
       <c r="F311" t="n">
         <v>3.153745072273324</v>
@@ -9788,7 +9788,7 @@
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>0.3161302506923676</v>
+        <v>0.6831950545310974</v>
       </c>
       <c r="F312" t="n">
         <v>12.68068331143232</v>
@@ -9818,7 +9818,7 @@
         <v>1</v>
       </c>
       <c r="E313" t="n">
-        <v>0.8789936304092407</v>
+        <v>0.9484890699386597</v>
       </c>
       <c r="F313" t="n">
         <v>10.87385019710907</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="E314" t="n">
-        <v>0.4524853229522705</v>
+        <v>0.5515395998954773</v>
       </c>
       <c r="F314" t="n">
         <v>6.964520367936925</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="E315" t="n">
-        <v>0.2498476207256317</v>
+        <v>0.4276494383811951</v>
       </c>
       <c r="F315" t="n">
         <v>3.120893561103811</v>
@@ -9908,7 +9908,7 @@
         <v>1</v>
       </c>
       <c r="E316" t="n">
-        <v>0.1385622471570969</v>
+        <v>0.3793797492980957</v>
       </c>
       <c r="F316" t="n">
         <v>41.36005256241787</v>
@@ -9938,7 +9938,7 @@
         <v>1</v>
       </c>
       <c r="E317" t="n">
-        <v>0.9695081114768982</v>
+        <v>0.9450764060020447</v>
       </c>
       <c r="F317" t="n">
         <v>9.395532194480946</v>
@@ -9968,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="E318" t="n">
-        <v>0.592642605304718</v>
+        <v>0.4647194445133209</v>
       </c>
       <c r="F318" t="n">
         <v>12.81208935611038</v>
@@ -9998,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="E319" t="n">
-        <v>0.5946609973907471</v>
+        <v>0.6822143793106079</v>
       </c>
       <c r="F319" t="n">
         <v>25.7227332457293</v>
@@ -10028,7 +10028,7 @@
         <v>0</v>
       </c>
       <c r="E320" t="n">
-        <v>0.3498236238956451</v>
+        <v>0.3886843025684357</v>
       </c>
       <c r="F320" t="n">
         <v>8.77207392197125</v>
@@ -10058,7 +10058,7 @@
         <v>0</v>
       </c>
       <c r="E321" t="n">
-        <v>0.8425021767616272</v>
+        <v>0.7751340270042419</v>
       </c>
       <c r="F321" t="n">
         <v>4.53388090349076</v>
@@ -10088,7 +10088,7 @@
         <v>1</v>
       </c>
       <c r="E322" t="n">
-        <v>0.4436156153678894</v>
+        <v>0.3439923822879791</v>
       </c>
       <c r="F322" t="n">
         <v>21.3223819301848</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="E323" t="n">
-        <v>0.008843684569001198</v>
+        <v>0.0939982607960701</v>
       </c>
       <c r="F323" t="n">
         <v>2.85831622176591</v>
@@ -10148,7 +10148,7 @@
         <v>0</v>
       </c>
       <c r="E324" t="n">
-        <v>0.7511609792709351</v>
+        <v>0.5920180678367615</v>
       </c>
       <c r="F324" t="n">
         <v>5.84804928131417</v>
@@ -10178,7 +10178,7 @@
         <v>1</v>
       </c>
       <c r="E325" t="n">
-        <v>0.8516915440559387</v>
+        <v>0.8583004474639893</v>
       </c>
       <c r="F325" t="n">
         <v>16.5913757700205</v>
@@ -10208,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="E326" t="n">
-        <v>0.1023541390895844</v>
+        <v>0.1722469627857208</v>
       </c>
       <c r="F326" t="n">
         <v>2.56262833675565</v>
@@ -10238,7 +10238,7 @@
         <v>0</v>
       </c>
       <c r="E327" t="n">
-        <v>0.3168425559997559</v>
+        <v>0.2881476581096649</v>
       </c>
       <c r="F327" t="n">
         <v>10.4804928131417</v>
@@ -10268,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="E328" t="n">
-        <v>0.1116874665021896</v>
+        <v>0.1554410457611084</v>
       </c>
       <c r="F328" t="n">
         <v>11.6632443531828</v>
@@ -10298,7 +10298,7 @@
         <v>0</v>
       </c>
       <c r="E329" t="n">
-        <v>0.06876229494810104</v>
+        <v>0.1651597768068314</v>
       </c>
       <c r="F329" t="n">
         <v>1.1170431211499</v>
@@ -10328,7 +10328,7 @@
         <v>0</v>
       </c>
       <c r="E330" t="n">
-        <v>0.7527782917022705</v>
+        <v>0.6142966151237488</v>
       </c>
       <c r="F330" t="n">
         <v>20.4681724845996</v>
@@ -10358,7 +10358,7 @@
         <v>1</v>
       </c>
       <c r="E331" t="n">
-        <v>0.6952934861183167</v>
+        <v>0.4141087234020233</v>
       </c>
       <c r="F331" t="n">
         <v>17.2813141683778</v>
@@ -10388,7 +10388,7 @@
         <v>0</v>
       </c>
       <c r="E332" t="n">
-        <v>0.127500906586647</v>
+        <v>0.132261261343956</v>
       </c>
       <c r="F332" t="n">
         <v>4.36960985626283</v>
@@ -10418,7 +10418,7 @@
         <v>1</v>
       </c>
       <c r="E333" t="n">
-        <v>0.5966593027114868</v>
+        <v>0.6421954035758972</v>
       </c>
       <c r="F333" t="n">
         <v>21.388090349076</v>
@@ -10448,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="E334" t="n">
-        <v>0.8031901717185974</v>
+        <v>0.828315258026123</v>
       </c>
       <c r="F334" t="n">
         <v>16.8213552361396</v>
@@ -10478,7 +10478,7 @@
         <v>1</v>
       </c>
       <c r="E335" t="n">
-        <v>0.009829670190811157</v>
+        <v>0.05231352150440216</v>
       </c>
       <c r="F335" t="n">
         <v>16.4599589322382</v>
@@ -10508,7 +10508,7 @@
         <v>0</v>
       </c>
       <c r="E336" t="n">
-        <v>0.841396689414978</v>
+        <v>0.6719724535942078</v>
       </c>
       <c r="F336" t="n">
         <v>17.7741273100616</v>
@@ -10538,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="E337" t="n">
-        <v>0.5626809597015381</v>
+        <v>0.3201262354850769</v>
       </c>
       <c r="F337" t="n">
         <v>4.8952772073922</v>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="E338" t="n">
-        <v>0.05815811455249786</v>
+        <v>0.130845695734024</v>
       </c>
       <c r="F338" t="n">
         <v>10.9075975359343</v>
@@ -10598,7 +10598,7 @@
         <v>0</v>
       </c>
       <c r="E339" t="n">
-        <v>0.492323249578476</v>
+        <v>0.4349536299705505</v>
       </c>
       <c r="F339" t="n">
         <v>6.73511293634497</v>
@@ -10628,7 +10628,7 @@
         <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>0.86360764503479</v>
+        <v>0.7891798615455627</v>
       </c>
       <c r="F340" t="n">
         <v>22.0780287474333</v>
@@ -10658,7 +10658,7 @@
         <v>0</v>
       </c>
       <c r="E341" t="n">
-        <v>0.3284900188446045</v>
+        <v>0.442504346370697</v>
       </c>
       <c r="F341" t="n">
         <v>2.8911704312115</v>
@@ -10688,7 +10688,7 @@
         <v>1</v>
       </c>
       <c r="E342" t="n">
-        <v>0.8395086526870728</v>
+        <v>0.7499369978904724</v>
       </c>
       <c r="F342" t="n">
         <v>23.3921971252567</v>
@@ -10718,7 +10718,7 @@
         <v>0</v>
       </c>
       <c r="E343" t="n">
-        <v>0.7199550271034241</v>
+        <v>0.6545122265815735</v>
       </c>
       <c r="F343" t="n">
         <v>14.7515400410678</v>
@@ -10748,7 +10748,7 @@
         <v>0</v>
       </c>
       <c r="E344" t="n">
-        <v>0.294380396604538</v>
+        <v>0.2945134937763214</v>
       </c>
       <c r="F344" t="n">
         <v>14.1273100616016</v>
@@ -10778,7 +10778,7 @@
         <v>0</v>
       </c>
       <c r="E345" t="n">
-        <v>0.2331779301166534</v>
+        <v>0.3990164399147034</v>
       </c>
       <c r="F345" t="n">
         <v>3.87679671457906</v>
@@ -10808,7 +10808,7 @@
         <v>0</v>
       </c>
       <c r="E346" t="n">
-        <v>0.181553527712822</v>
+        <v>0.245373323559761</v>
       </c>
       <c r="F346" t="n">
         <v>2.13552361396304</v>
@@ -10838,7 +10838,7 @@
         <v>0</v>
       </c>
       <c r="E347" t="n">
-        <v>0.1604742705821991</v>
+        <v>0.3537714779376984</v>
       </c>
       <c r="F347" t="n">
         <v>10.2505133470226</v>
@@ -10868,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="E348" t="n">
-        <v>0.797747015953064</v>
+        <v>0.6026221513748169</v>
       </c>
       <c r="F348" t="n">
         <v>22.8336755646817</v>
@@ -10898,7 +10898,7 @@
         <v>1</v>
       </c>
       <c r="E349" t="n">
-        <v>0.6948888897895813</v>
+        <v>0.6185023784637451</v>
       </c>
       <c r="F349" t="n">
         <v>12.8131416837782</v>
@@ -10928,7 +10928,7 @@
         <v>0</v>
       </c>
       <c r="E350" t="n">
-        <v>0.08019884675741196</v>
+        <v>0.1863787025213242</v>
       </c>
       <c r="F350" t="n">
         <v>2.75975359342916</v>
@@ -10958,7 +10958,7 @@
         <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>0.01178773771971464</v>
+        <v>0.08661648631095886</v>
       </c>
       <c r="F351" t="n">
         <v>3.71252566735113</v>
@@ -10988,7 +10988,7 @@
         <v>0</v>
       </c>
       <c r="E352" t="n">
-        <v>0.03249975293874741</v>
+        <v>0.1082057654857635</v>
       </c>
       <c r="F352" t="n">
         <v>2.13552361396304</v>
@@ -11018,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="E353" t="n">
-        <v>0.2686529755592346</v>
+        <v>0.2763841450214386</v>
       </c>
       <c r="F353" t="n">
         <v>7.95071868583162</v>
@@ -11048,7 +11048,7 @@
         <v>0</v>
       </c>
       <c r="E354" t="n">
-        <v>0.4813860952854156</v>
+        <v>0.4457701444625854</v>
       </c>
       <c r="F354" t="n">
         <v>5.88090349075975</v>
@@ -11078,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="E355" t="n">
-        <v>0.9317665100097656</v>
+        <v>0.9058096408843994</v>
       </c>
       <c r="F355" t="n">
         <v>12.7145790554415</v>
@@ -11108,7 +11108,7 @@
         <v>0</v>
       </c>
       <c r="E356" t="n">
-        <v>0.1233468055725098</v>
+        <v>0.2014688700437546</v>
       </c>
       <c r="F356" t="n">
         <v>3.61396303901437</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="E357" t="n">
-        <v>0.1006561443209648</v>
+        <v>0.1434576213359833</v>
       </c>
       <c r="F357" t="n">
         <v>1.44558521560575</v>
@@ -11168,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="E358" t="n">
-        <v>0.1248612180352211</v>
+        <v>0.3036318719387054</v>
       </c>
       <c r="F358" t="n">
         <v>16.4599589322382</v>
@@ -11198,7 +11198,7 @@
         <v>0</v>
       </c>
       <c r="E359" t="n">
-        <v>0.8615249991416931</v>
+        <v>0.8087257146835327</v>
       </c>
       <c r="F359" t="n">
         <v>10.5790554414784</v>
@@ -11228,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="E360" t="n">
-        <v>0.7628014087677002</v>
+        <v>0.6995646953582764</v>
       </c>
       <c r="F360" t="n">
         <v>7.06365503080082</v>
@@ -11258,7 +11258,7 @@
         <v>1</v>
       </c>
       <c r="E361" t="n">
-        <v>0.3648865818977356</v>
+        <v>0.3524216413497925</v>
       </c>
       <c r="F361" t="n">
         <v>20.5667351129363</v>
@@ -11288,7 +11288,7 @@
         <v>0</v>
       </c>
       <c r="E362" t="n">
-        <v>0.04741470515727997</v>
+        <v>0.3368192911148071</v>
       </c>
       <c r="F362" t="n">
         <v>14.9815195071869</v>
@@ -11318,7 +11318,7 @@
         <v>0</v>
       </c>
       <c r="E363" t="n">
-        <v>0.7007988095283508</v>
+        <v>0.6108826994895935</v>
       </c>
       <c r="F363" t="n">
         <v>3.87679671457906</v>
@@ -11348,7 +11348,7 @@
         <v>0</v>
       </c>
       <c r="E364" t="n">
-        <v>0.2616645395755768</v>
+        <v>0.2604261934757233</v>
       </c>
       <c r="F364" t="n">
         <v>3.18685831622177</v>
@@ -11378,7 +11378,7 @@
         <v>0</v>
       </c>
       <c r="E365" t="n">
-        <v>0.1071634665131569</v>
+        <v>0.2167786210775375</v>
       </c>
       <c r="F365" t="n">
         <v>3.44969199178645</v>
@@ -11408,7 +11408,7 @@
         <v>1</v>
       </c>
       <c r="E366" t="n">
-        <v>0.8902939558029175</v>
+        <v>0.8292762041091919</v>
       </c>
       <c r="F366" t="n">
         <v>21.6180698151951</v>
@@ -11438,7 +11438,7 @@
         <v>0</v>
       </c>
       <c r="E367" t="n">
-        <v>0.3589241802692413</v>
+        <v>0.3649890720844269</v>
       </c>
       <c r="F367" t="n">
         <v>20.2710472279261</v>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="E368" t="n">
-        <v>0.6766249537467957</v>
+        <v>0.6349965929985046</v>
       </c>
       <c r="F368" t="n">
         <v>6.27515400410678</v>
@@ -11498,7 +11498,7 @@
         <v>0</v>
       </c>
       <c r="E369" t="n">
-        <v>0.2159287631511688</v>
+        <v>0.3538064956665039</v>
       </c>
       <c r="F369" t="n">
         <v>3.61396303901437</v>
@@ -11528,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="E370" t="n">
-        <v>0.4863730370998383</v>
+        <v>0.4839452803134918</v>
       </c>
       <c r="F370" t="n">
         <v>7.85215605749487</v>
@@ -11558,7 +11558,7 @@
         <v>1</v>
       </c>
       <c r="E371" t="n">
-        <v>0.8823239207267761</v>
+        <v>0.8051588535308838</v>
       </c>
       <c r="F371" t="n">
         <v>23.129363449692</v>
@@ -11588,7 +11588,7 @@
         <v>0</v>
       </c>
       <c r="E372" t="n">
-        <v>0.7735027074813843</v>
+        <v>0.739966869354248</v>
       </c>
       <c r="F372" t="n">
         <v>5.38809034907598</v>
@@ -11618,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="E373" t="n">
-        <v>0.1850729286670685</v>
+        <v>0.3959112465381622</v>
       </c>
       <c r="F373" t="n">
         <v>14.1273100616016</v>
@@ -11648,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="E374" t="n">
-        <v>0.01094493363052607</v>
+        <v>0.1284152269363403</v>
       </c>
       <c r="F374" t="n">
         <v>2.43121149897331</v>
@@ -11678,7 +11678,7 @@
         <v>0</v>
       </c>
       <c r="E375" t="n">
-        <v>0.0137395104393363</v>
+        <v>0.1925825178623199</v>
       </c>
       <c r="F375" t="n">
         <v>9.757700205338811</v>
@@ -11708,7 +11708,7 @@
         <v>0</v>
       </c>
       <c r="E376" t="n">
-        <v>0.1369327455759048</v>
+        <v>0.1938772350549698</v>
       </c>
       <c r="F376" t="n">
         <v>7.91786447638604</v>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="E377" t="n">
-        <v>0.6135157942771912</v>
+        <v>0.5440928339958191</v>
       </c>
       <c r="F377" t="n">
         <v>3.1211498973306</v>
@@ -11768,7 +11768,7 @@
         <v>0</v>
       </c>
       <c r="E378" t="n">
-        <v>0.08829817920923233</v>
+        <v>0.313015878200531</v>
       </c>
       <c r="F378" t="n">
         <v>11.1047227926078</v>
@@ -11798,7 +11798,7 @@
         <v>1</v>
       </c>
       <c r="E379" t="n">
-        <v>0.136755108833313</v>
+        <v>0.3120085299015045</v>
       </c>
       <c r="F379" t="n">
         <v>24.476386036961</v>
@@ -11828,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="E380" t="n">
-        <v>0.3240967690944672</v>
+        <v>0.2575852572917938</v>
       </c>
       <c r="F380" t="n">
         <v>68.90958904</v>
@@ -11858,7 +11858,7 @@
         <v>0</v>
       </c>
       <c r="E381" t="n">
-        <v>0.4888648390769958</v>
+        <v>0.4810607135295868</v>
       </c>
       <c r="F381" t="n">
         <v>6.570841889</v>
@@ -11888,7 +11888,7 @@
         <v>1</v>
       </c>
       <c r="E382" t="n">
-        <v>0.8869461417198181</v>
+        <v>0.9599863290786743</v>
       </c>
       <c r="F382" t="n">
         <v>51.05544148</v>
@@ -11918,7 +11918,7 @@
         <v>1</v>
       </c>
       <c r="E383" t="n">
-        <v>0.666308581829071</v>
+        <v>0.649812638759613</v>
       </c>
       <c r="F383" t="n">
         <v>41.92197125</v>
@@ -11948,7 +11948,7 @@
         <v>1</v>
       </c>
       <c r="E384" t="n">
-        <v>0.3427074551582336</v>
+        <v>0.3119026124477386</v>
       </c>
       <c r="F384" t="n">
         <v>16.91991786</v>
@@ -11978,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="E385" t="n">
-        <v>0.638028085231781</v>
+        <v>0.6619081497192383</v>
       </c>
       <c r="F385" t="n">
         <v>33.44558522</v>
@@ -12008,7 +12008,7 @@
         <v>1</v>
       </c>
       <c r="E386" t="n">
-        <v>0.3401886224746704</v>
+        <v>0.3569130301475525</v>
       </c>
       <c r="F386" t="n">
         <v>14.42299795</v>
@@ -12038,7 +12038,7 @@
         <v>1</v>
       </c>
       <c r="E387" t="n">
-        <v>0.4558960795402527</v>
+        <v>0.4533431828022003</v>
       </c>
       <c r="F387" t="n">
         <v>42.38193019</v>
@@ -12068,7 +12068,7 @@
         <v>0</v>
       </c>
       <c r="E388" t="n">
-        <v>0.3934962153434753</v>
+        <v>0.3996652066707611</v>
       </c>
       <c r="F388" t="n">
         <v>29.73305955</v>
@@ -12098,7 +12098,7 @@
         <v>0</v>
       </c>
       <c r="E389" t="n">
-        <v>0.3149441480636597</v>
+        <v>0.4220141470432281</v>
       </c>
       <c r="F389" t="n">
         <v>5.092402464</v>
@@ -12128,7 +12128,7 @@
         <v>0</v>
       </c>
       <c r="E390" t="n">
-        <v>0.238071620464325</v>
+        <v>0.2843427658081055</v>
       </c>
       <c r="F390" t="n">
         <v>5.519507187</v>
@@ -12158,7 +12158,7 @@
         <v>0</v>
       </c>
       <c r="E391" t="n">
-        <v>0.3712673485279083</v>
+        <v>0.4796597957611084</v>
       </c>
       <c r="F391" t="n">
         <v>3.54825462</v>
@@ -12188,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="E392" t="n">
-        <v>0.4639870822429657</v>
+        <v>0.4883944392204285</v>
       </c>
       <c r="F392" t="n">
         <v>12.74743327</v>
@@ -12218,7 +12218,7 @@
         <v>1</v>
       </c>
       <c r="E393" t="n">
-        <v>0.3537082970142365</v>
+        <v>0.3062261939048767</v>
       </c>
       <c r="F393" t="n">
         <v>57.06776181</v>
@@ -12248,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="E394" t="n">
-        <v>0.2488690167665482</v>
+        <v>0.1670991778373718</v>
       </c>
       <c r="F394" t="n">
         <v>8.147843943</v>
@@ -12278,7 +12278,7 @@
         <v>0</v>
       </c>
       <c r="E395" t="n">
-        <v>0.4122675061225891</v>
+        <v>0.5741777420043945</v>
       </c>
       <c r="F395" t="n">
         <v>8.213552361</v>
@@ -12308,7 +12308,7 @@
         <v>1</v>
       </c>
       <c r="E396" t="n">
-        <v>0.4624493718147278</v>
+        <v>0.5244269371032715</v>
       </c>
       <c r="F396" t="n">
         <v>46.48870637</v>
@@ -12338,7 +12338,7 @@
         <v>0</v>
       </c>
       <c r="E397" t="n">
-        <v>0.3267424702644348</v>
+        <v>0.4046098589897156</v>
       </c>
       <c r="F397" t="n">
         <v>1.577002053</v>
@@ -12368,7 +12368,7 @@
         <v>0</v>
       </c>
       <c r="E398" t="n">
-        <v>0.4093882739543915</v>
+        <v>0.4619887173175812</v>
       </c>
       <c r="F398" t="n">
         <v>34.03696099</v>
@@ -12398,7 +12398,7 @@
         <v>0</v>
       </c>
       <c r="E399" t="n">
-        <v>0.2534441351890564</v>
+        <v>0.1937438249588013</v>
       </c>
       <c r="F399" t="n">
         <v>13.33880904</v>
@@ -12428,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="E400" t="n">
-        <v>0.8351117372512817</v>
+        <v>0.9098537564277649</v>
       </c>
       <c r="F400" t="n">
         <v>44.58316222</v>
@@ -12458,7 +12458,7 @@
         <v>1</v>
       </c>
       <c r="E401" t="n">
-        <v>0.6187347769737244</v>
+        <v>0.5292245149612427</v>
       </c>
       <c r="F401" t="n">
         <v>40.31211499</v>
@@ -12488,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="E402" t="n">
-        <v>0.6434251070022583</v>
+        <v>0.6478416323661804</v>
       </c>
       <c r="F402" t="n">
         <v>5.585215606</v>
@@ -12518,7 +12518,7 @@
         <v>0</v>
       </c>
       <c r="E403" t="n">
-        <v>0.6573659181594849</v>
+        <v>0.6308000087738037</v>
       </c>
       <c r="F403" t="n">
         <v>8.706365503000001</v>
@@ -12548,7 +12548,7 @@
         <v>1</v>
       </c>
       <c r="E404" t="n">
-        <v>0.9384306073188782</v>
+        <v>0.9558690190315247</v>
       </c>
       <c r="F404" t="n">
         <v>33.64271047</v>
@@ -12578,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="E405" t="n">
-        <v>0.23517906665802</v>
+        <v>0.203387662768364</v>
       </c>
       <c r="F405" t="n">
         <v>33.69863014</v>
@@ -12608,7 +12608,7 @@
         <v>0</v>
       </c>
       <c r="E406" t="n">
-        <v>0.2409051358699799</v>
+        <v>0.2894425392150879</v>
       </c>
       <c r="F406" t="n">
         <v>1.347945205</v>
@@ -12638,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="E407" t="n">
-        <v>0.01920623704791069</v>
+        <v>0.08453676849603653</v>
       </c>
       <c r="F407" t="n">
         <v>37.42094456</v>
@@ -12668,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="E408" t="n">
-        <v>0.05869023874402046</v>
+        <v>0.1144284531474113</v>
       </c>
       <c r="F408" t="n">
         <v>17.11704312</v>
@@ -12698,7 +12698,7 @@
         <v>1</v>
       </c>
       <c r="E409" t="n">
-        <v>0.5278557538986206</v>
+        <v>0.4865110814571381</v>
       </c>
       <c r="F409" t="n">
         <v>25.62628337</v>
@@ -12728,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="E410" t="n">
-        <v>0.5256452560424805</v>
+        <v>0.5426017045974731</v>
       </c>
       <c r="F410" t="n">
         <v>1.544147844</v>
@@ -12758,7 +12758,7 @@
         <v>1</v>
       </c>
       <c r="E411" t="n">
-        <v>0.267568439245224</v>
+        <v>0.3248752355575562</v>
       </c>
       <c r="F411" t="n">
         <v>28.45174538</v>
@@ -12788,7 +12788,7 @@
         <v>1</v>
       </c>
       <c r="E412" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.6872466802597046</v>
       </c>
       <c r="F412" t="n">
         <v>27.36755647</v>
@@ -12818,7 +12818,7 @@
         <v>1</v>
       </c>
       <c r="E413" t="n">
-        <v>0.578010082244873</v>
+        <v>0.5459107160568237</v>
       </c>
       <c r="F413" t="n">
         <v>27.36755647</v>
@@ -12848,7 +12848,7 @@
         <v>0</v>
       </c>
       <c r="E414" t="n">
-        <v>0.9502986073493958</v>
+        <v>0.8334992527961731</v>
       </c>
       <c r="F414" t="n">
         <v>6.373716632</v>
@@ -12878,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="E415" t="n">
-        <v>0.939552366733551</v>
+        <v>0.9393029808998108</v>
       </c>
       <c r="F415" t="n">
         <v>8.936344969</v>
@@ -12908,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="E416" t="n">
-        <v>0.3986816108226776</v>
+        <v>0.3575111329555511</v>
       </c>
       <c r="F416" t="n">
         <v>20.56673511</v>
@@ -12938,7 +12938,7 @@
         <v>1</v>
       </c>
       <c r="E417" t="n">
-        <v>0.2050686329603195</v>
+        <v>0.2176931798458099</v>
       </c>
       <c r="F417" t="n">
         <v>29.76591376</v>
@@ -12968,7 +12968,7 @@
         <v>0</v>
       </c>
       <c r="E418" t="n">
-        <v>0.4458589553833008</v>
+        <v>0.4487431049346924</v>
       </c>
       <c r="F418" t="n">
         <v>32.03285421</v>
@@ -12998,7 +12998,7 @@
         <v>0</v>
       </c>
       <c r="E419" t="n">
-        <v>0.3436390459537506</v>
+        <v>0.3424834311008453</v>
       </c>
       <c r="F419" t="n">
         <v>11.26899384</v>
@@ -13028,7 +13028,7 @@
         <v>1</v>
       </c>
       <c r="E420" t="n">
-        <v>0.6167758703231812</v>
+        <v>0.5720916986465454</v>
       </c>
       <c r="F420" t="n">
         <v>19.71252567</v>
@@ -13058,7 +13058,7 @@
         <v>1</v>
       </c>
       <c r="E421" t="n">
-        <v>0.9282248020172119</v>
+        <v>0.9092174768447876</v>
       </c>
       <c r="F421" t="n">
         <v>50.82546201</v>
@@ -13088,7 +13088,7 @@
         <v>0</v>
       </c>
       <c r="E422" t="n">
-        <v>0.1186397969722748</v>
+        <v>0.2302688807249069</v>
       </c>
       <c r="F422" t="n">
         <v>9.954825462000001</v>
@@ -13118,7 +13118,7 @@
         <v>1</v>
       </c>
       <c r="E423" t="n">
-        <v>0.4115019142627716</v>
+        <v>0.3903165459632874</v>
       </c>
       <c r="F423" t="n">
         <v>8.837782341</v>
@@ -13148,7 +13148,7 @@
         <v>0</v>
       </c>
       <c r="E424" t="n">
-        <v>0.14949731528759</v>
+        <v>0.2557871341705322</v>
       </c>
       <c r="F424" t="n">
         <v>27.79466119</v>
@@ -13178,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="E425" t="n">
-        <v>0.6276854872703552</v>
+        <v>0.5522857904434204</v>
       </c>
       <c r="F425" t="n">
         <v>29.27310062</v>
@@ -13208,7 +13208,7 @@
         <v>0</v>
       </c>
       <c r="E426" t="n">
-        <v>0.527233898639679</v>
+        <v>0.4889319837093353</v>
       </c>
       <c r="F426" t="n">
         <v>14.58726899</v>
@@ -13238,7 +13238,7 @@
         <v>1</v>
       </c>
       <c r="E427" t="n">
-        <v>0.5408005118370056</v>
+        <v>0.5006591081619263</v>
       </c>
       <c r="F427" t="n">
         <v>41.49486653</v>
@@ -13268,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="E428" t="n">
-        <v>0.6950123906135559</v>
+        <v>0.6266912817955017</v>
       </c>
       <c r="F428" t="n">
         <v>31.6386037</v>
@@ -13298,7 +13298,7 @@
         <v>0</v>
       </c>
       <c r="E429" t="n">
-        <v>0.0003071363316848874</v>
+        <v>0.009422398172318935</v>
       </c>
       <c r="F429" t="n">
         <v>1.314168378</v>
@@ -13328,7 +13328,7 @@
         <v>0</v>
       </c>
       <c r="E430" t="n">
-        <v>0.5127164721488953</v>
+        <v>0.4625895321369171</v>
       </c>
       <c r="F430" t="n">
         <v>22.43942505</v>
@@ -13358,7 +13358,7 @@
         <v>1</v>
       </c>
       <c r="E431" t="n">
-        <v>0.196386530995369</v>
+        <v>0.1480340510606766</v>
       </c>
       <c r="F431" t="n">
         <v>15.17739816031537</v>
@@ -13388,7 +13388,7 @@
         <v>1</v>
       </c>
       <c r="E432" t="n">
-        <v>0.6416739225387573</v>
+        <v>0.6712132692337036</v>
       </c>
       <c r="F432" t="n">
         <v>16.75427069645204</v>
@@ -13418,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="E433" t="n">
-        <v>0.1287644058465958</v>
+        <v>0.1047776266932487</v>
       </c>
       <c r="F433" t="n">
         <v>36.39947437582128</v>
@@ -13448,7 +13448,7 @@
         <v>0</v>
       </c>
       <c r="E434" t="n">
-        <v>0.1660573184490204</v>
+        <v>0.2280934154987335</v>
       </c>
       <c r="F434" t="n">
         <v>18.39684625492773</v>
@@ -13478,7 +13478,7 @@
         <v>0</v>
       </c>
       <c r="E435" t="n">
-        <v>0.7376783490180969</v>
+        <v>0.7830931544303894</v>
       </c>
       <c r="F435" t="n">
         <v>8.902759526938238</v>
@@ -13508,7 +13508,7 @@
         <v>1</v>
       </c>
       <c r="E436" t="n">
-        <v>0.8032366037368774</v>
+        <v>0.8273919224739075</v>
       </c>
       <c r="F436" t="n">
         <v>19.2838370565046</v>
@@ -13538,7 +13538,7 @@
         <v>1</v>
       </c>
       <c r="E437" t="n">
-        <v>0.6699564456939697</v>
+        <v>0.7494838833808899</v>
       </c>
       <c r="F437" t="n">
         <v>20.26938239159001</v>
@@ -13568,7 +13568,7 @@
         <v>1</v>
       </c>
       <c r="E438" t="n">
-        <v>0.7547039389610291</v>
+        <v>0.8014979958534241</v>
       </c>
       <c r="F438" t="n">
         <v>8.869908015768726</v>
@@ -13598,7 +13598,7 @@
         <v>0</v>
       </c>
       <c r="E439" t="n">
-        <v>0.5820385813713074</v>
+        <v>0.6375153064727783</v>
       </c>
       <c r="F439" t="n">
         <v>4.139290407358739</v>
@@ -13628,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="E440" t="n">
-        <v>0.8797136545181274</v>
+        <v>0.8963819742202759</v>
       </c>
       <c r="F440" t="n">
         <v>6.537450722733245</v>
@@ -13658,7 +13658,7 @@
         <v>0</v>
       </c>
       <c r="E441" t="n">
-        <v>0.5249747037887573</v>
+        <v>0.6135026216506958</v>
       </c>
       <c r="F441" t="n">
         <v>6.176084099868594</v>
@@ -13688,7 +13688,7 @@
         <v>0</v>
       </c>
       <c r="E442" t="n">
-        <v>0.5033729076385498</v>
+        <v>0.5069555640220642</v>
       </c>
       <c r="F442" t="n">
         <v>5.256241787122208</v>
@@ -13718,7 +13718,7 @@
         <v>0</v>
       </c>
       <c r="E443" t="n">
-        <v>0.4498839378356934</v>
+        <v>0.4895459115505219</v>
       </c>
       <c r="F443" t="n">
         <v>3.252299605781866</v>
@@ -13748,7 +13748,7 @@
         <v>1</v>
       </c>
       <c r="E444" t="n">
-        <v>0.2132160365581512</v>
+        <v>0.3138687014579773</v>
       </c>
       <c r="F444" t="n">
         <v>9.888304862023652</v>
@@ -13778,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="E445" t="n">
-        <v>0.08942855894565582</v>
+        <v>0.1678762584924698</v>
       </c>
       <c r="F445" t="n">
         <v>34.92115637319316</v>
@@ -13808,7 +13808,7 @@
         <v>1</v>
       </c>
       <c r="E446" t="n">
-        <v>0.6171317100524902</v>
+        <v>0.620614230632782</v>
       </c>
       <c r="F446" t="n">
         <v>21.4209445585216</v>
@@ -13838,7 +13838,7 @@
         <v>0</v>
       </c>
       <c r="E447" t="n">
-        <v>0.6098337173461914</v>
+        <v>0.521446168422699</v>
       </c>
       <c r="F447" t="n">
         <v>9.002053388090349</v>
@@ -13868,7 +13868,7 @@
         <v>0</v>
       </c>
       <c r="E448" t="n">
-        <v>0.2510403096675873</v>
+        <v>0.1636468172073364</v>
       </c>
       <c r="F448" t="n">
         <v>3.51540041067762</v>
@@ -13898,7 +13898,7 @@
         <v>0</v>
       </c>
       <c r="E449" t="n">
-        <v>0.287769079208374</v>
+        <v>0.2093686759471893</v>
       </c>
       <c r="F449" t="n">
         <v>5.71663244353183</v>
@@ -13928,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="E450" t="n">
-        <v>0.09399596601724625</v>
+        <v>0.06971410661935806</v>
       </c>
       <c r="F450" t="n">
         <v>22.3737166324435</v>
@@ -13958,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="E451" t="n">
-        <v>0.1306594014167786</v>
+        <v>0.08531826734542847</v>
       </c>
       <c r="F451" t="n">
         <v>9.232032854209439</v>
@@ -13988,7 +13988,7 @@
         <v>0</v>
       </c>
       <c r="E452" t="n">
-        <v>0.04687562584877014</v>
+        <v>0.09049148112535477</v>
       </c>
       <c r="F452" t="n">
         <v>8.08213552361396</v>
@@ -14018,7 +14018,7 @@
         <v>0</v>
       </c>
       <c r="E453" t="n">
-        <v>0.3649828732013702</v>
+        <v>0.2909984886646271</v>
       </c>
       <c r="F453" t="n">
         <v>15.3100616016427</v>
@@ -14048,7 +14048,7 @@
         <v>1</v>
       </c>
       <c r="E454" t="n">
-        <v>0.8671075105667114</v>
+        <v>0.8954935073852539</v>
       </c>
       <c r="F454" t="n">
         <v>17.1170431211499</v>
@@ -14078,7 +14078,7 @@
         <v>0</v>
       </c>
       <c r="E455" t="n">
-        <v>0.05730006843805313</v>
+        <v>0.0632009282708168</v>
       </c>
       <c r="F455" t="n">
         <v>8.279260780287469</v>
@@ -14108,7 +14108,7 @@
         <v>0</v>
       </c>
       <c r="E456" t="n">
-        <v>0.248082235455513</v>
+        <v>0.1740035265684128</v>
       </c>
       <c r="F456" t="n">
         <v>23.8193018480493</v>
@@ -14138,7 +14138,7 @@
         <v>0</v>
       </c>
       <c r="E457" t="n">
-        <v>0.414851039648056</v>
+        <v>0.2699321210384369</v>
       </c>
       <c r="F457" t="n">
         <v>17.9055441478439</v>
@@ -14168,7 +14168,7 @@
         <v>0</v>
       </c>
       <c r="E458" t="n">
-        <v>0.3511398732662201</v>
+        <v>0.4176812469959259</v>
       </c>
       <c r="F458" t="n">
         <v>16.0328542094456</v>
@@ -14198,7 +14198,7 @@
         <v>1</v>
       </c>
       <c r="E459" t="n">
-        <v>0.418805867433548</v>
+        <v>0.2536575198173523</v>
       </c>
       <c r="F459" t="n">
         <v>17.2813141683778</v>
@@ -14228,7 +14228,7 @@
         <v>0</v>
       </c>
       <c r="E460" t="n">
-        <v>0.4175386428833008</v>
+        <v>0.3112647831439972</v>
       </c>
       <c r="F460" t="n">
         <v>17.9712525667351</v>
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="E461" t="n">
-        <v>0.6749529838562012</v>
+        <v>0.6015855073928833</v>
       </c>
       <c r="F461" t="n">
         <v>18.7268993839836</v>
@@ -14288,7 +14288,7 @@
         <v>0</v>
       </c>
       <c r="E462" t="n">
-        <v>0.3655238747596741</v>
+        <v>0.3068671226501465</v>
       </c>
       <c r="F462" t="n">
         <v>9.85626283367557</v>
@@ -14318,7 +14318,7 @@
         <v>0</v>
       </c>
       <c r="E463" t="n">
-        <v>0.4508316814899445</v>
+        <v>0.3289051055908203</v>
       </c>
       <c r="F463" t="n">
         <v>7.45790554414784</v>
@@ -14348,7 +14348,7 @@
         <v>1</v>
       </c>
       <c r="E464" t="n">
-        <v>0.9854117035865784</v>
+        <v>0.9381745457649231</v>
       </c>
       <c r="F464" t="n">
         <v>15.7043121149897</v>
@@ -14378,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="E465" t="n">
-        <v>0.4090254902839661</v>
+        <v>0.3698793947696686</v>
       </c>
       <c r="F465" t="n">
         <v>3.84394250513347</v>
@@ -14408,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="E466" t="n">
-        <v>0.2998137772083282</v>
+        <v>0.1614113450050354</v>
       </c>
       <c r="F466" t="n">
         <v>7.22792607802875</v>
@@ -14438,7 +14438,7 @@
         <v>1</v>
       </c>
       <c r="E467" t="n">
-        <v>0.8664277791976929</v>
+        <v>0.7877466082572937</v>
       </c>
       <c r="F467" t="n">
         <v>20.6324435318275</v>
@@ -14468,7 +14468,7 @@
         <v>1</v>
       </c>
       <c r="E468" t="n">
-        <v>0.6794993281364441</v>
+        <v>0.5857872366905212</v>
       </c>
       <c r="F468" t="n">
         <v>16.5913757700205</v>
@@ -14498,7 +14498,7 @@
         <v>0</v>
       </c>
       <c r="E469" t="n">
-        <v>0.09270317852497101</v>
+        <v>0.1678098738193512</v>
       </c>
       <c r="F469" t="n">
         <v>6.80082135523614</v>
@@ -14528,7 +14528,7 @@
         <v>0</v>
       </c>
       <c r="E470" t="n">
-        <v>0.5037936568260193</v>
+        <v>0.4552769958972931</v>
       </c>
       <c r="F470" t="n">
         <v>16.2628336755647</v>
@@ -14558,7 +14558,7 @@
         <v>0</v>
       </c>
       <c r="E471" t="n">
-        <v>0.02075787447392941</v>
+        <v>0.08923044055700302</v>
       </c>
       <c r="F471" t="n">
         <v>22.1108829568789</v>
@@ -14588,7 +14588,7 @@
         <v>0</v>
       </c>
       <c r="E472" t="n">
-        <v>0.1281967908143997</v>
+        <v>0.101920023560524</v>
       </c>
       <c r="F472" t="n">
         <v>11.9260780287474</v>
@@ -14618,7 +14618,7 @@
         <v>0</v>
       </c>
       <c r="E473" t="n">
-        <v>0.2264039516448975</v>
+        <v>0.166614443063736</v>
       </c>
       <c r="F473" t="n">
         <v>2.6611909650924</v>
@@ -14648,7 +14648,7 @@
         <v>0</v>
       </c>
       <c r="E474" t="n">
-        <v>0.01376340445131063</v>
+        <v>0.06437680870294571</v>
       </c>
       <c r="F474" t="n">
         <v>12.7145790554415</v>
@@ -14678,7 +14678,7 @@
         <v>1</v>
       </c>
       <c r="E475" t="n">
-        <v>0.6691603660583496</v>
+        <v>0.6599624156951904</v>
       </c>
       <c r="F475" t="n">
         <v>21.223819301848</v>
@@ -14708,7 +14708,7 @@
         <v>0</v>
       </c>
       <c r="E476" t="n">
-        <v>0.02730698324739933</v>
+        <v>0.07438658177852631</v>
       </c>
       <c r="F476" t="n">
         <v>14.7515400410678</v>
@@ -14738,7 +14738,7 @@
         <v>1</v>
       </c>
       <c r="E477" t="n">
-        <v>0.8542637825012207</v>
+        <v>0.8383896350860596</v>
       </c>
       <c r="F477" t="n">
         <v>23.1622176591376</v>
@@ -14768,7 +14768,7 @@
         <v>0</v>
       </c>
       <c r="E478" t="n">
-        <v>0.5220036506652832</v>
+        <v>0.4182083904743195</v>
       </c>
       <c r="F478" t="n">
         <v>15.6714579055441</v>
@@ -14798,7 +14798,7 @@
         <v>0</v>
       </c>
       <c r="E479" t="n">
-        <v>0.56308913230896</v>
+        <v>0.493365466594696</v>
       </c>
       <c r="F479" t="n">
         <v>7.62217659137577</v>
@@ -14828,7 +14828,7 @@
         <v>0</v>
       </c>
       <c r="E480" t="n">
-        <v>0.4020026922225952</v>
+        <v>0.2496959418058395</v>
       </c>
       <c r="F480" t="n">
         <v>15.4086242299795</v>
@@ -14858,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="E481" t="n">
-        <v>0.2141369134187698</v>
+        <v>0.1727335453033447</v>
       </c>
       <c r="F481" t="n">
         <v>0.5585215605749489</v>
@@ -14888,7 +14888,7 @@
         <v>0</v>
       </c>
       <c r="E482" t="n">
-        <v>0.5364930033683777</v>
+        <v>0.4981062412261963</v>
       </c>
       <c r="F482" t="n">
         <v>3.25256673511294</v>
@@ -14918,7 +14918,7 @@
         <v>0</v>
       </c>
       <c r="E483" t="n">
-        <v>0.8583948612213135</v>
+        <v>0.8531461954116821</v>
       </c>
       <c r="F483" t="n">
         <v>5.51950718685832</v>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="E484" t="n">
-        <v>0.171573132276535</v>
+        <v>0.1564876735210419</v>
       </c>
       <c r="F484" t="n">
         <v>23.3264887063655</v>
@@ -14978,7 +14978,7 @@
         <v>1</v>
       </c>
       <c r="E485" t="n">
-        <v>0.7560263872146606</v>
+        <v>0.599138081073761</v>
       </c>
       <c r="F485" t="n">
         <v>22.735112936345</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="E486" t="n">
-        <v>0.02430009841918945</v>
+        <v>0.06878655403852463</v>
       </c>
       <c r="F486" t="n">
         <v>2.75975359342916</v>
@@ -15038,7 +15038,7 @@
         <v>0</v>
       </c>
       <c r="E487" t="n">
-        <v>0.2687526345252991</v>
+        <v>0.1995175033807755</v>
       </c>
       <c r="F487" t="n">
         <v>2.72689938398357</v>
@@ -15068,7 +15068,7 @@
         <v>0</v>
       </c>
       <c r="E488" t="n">
-        <v>0.1852980703115463</v>
+        <v>0.1087641343474388</v>
       </c>
       <c r="F488" t="n">
         <v>8.016427104722791</v>
@@ -15098,7 +15098,7 @@
         <v>0</v>
       </c>
       <c r="E489" t="n">
-        <v>0.2356099337339401</v>
+        <v>0.1333643049001694</v>
       </c>
       <c r="F489" t="n">
         <v>5.65092402464066</v>
@@ -15128,7 +15128,7 @@
         <v>0</v>
       </c>
       <c r="E490" t="n">
-        <v>0.1744871586561203</v>
+        <v>0.1921495646238327</v>
       </c>
       <c r="F490" t="n">
         <v>2.52977412731006</v>
@@ -15158,7 +15158,7 @@
         <v>0</v>
       </c>
       <c r="E491" t="n">
-        <v>0.4104314744472504</v>
+        <v>0.1752341538667679</v>
       </c>
       <c r="F491" t="n">
         <v>3.1211498973306</v>
@@ -15188,7 +15188,7 @@
         <v>1</v>
       </c>
       <c r="E492" t="n">
-        <v>0.8770442605018616</v>
+        <v>0.8854837417602539</v>
       </c>
       <c r="F492" t="n">
         <v>17.2156057494867</v>
@@ -15218,7 +15218,7 @@
         <v>1</v>
       </c>
       <c r="E493" t="n">
-        <v>0.9805980324745178</v>
+        <v>0.942983090877533</v>
       </c>
       <c r="F493" t="n">
         <v>21.5852156057495</v>
@@ -15248,7 +15248,7 @@
         <v>0</v>
       </c>
       <c r="E494" t="n">
-        <v>0.5487655997276306</v>
+        <v>0.3448484539985657</v>
       </c>
       <c r="F494" t="n">
         <v>21.1581108829569</v>
@@ -15278,7 +15278,7 @@
         <v>0</v>
       </c>
       <c r="E495" t="n">
-        <v>0.2807802855968475</v>
+        <v>0.1313389092683792</v>
       </c>
       <c r="F495" t="n">
         <v>2.06981519507187</v>
@@ -15308,7 +15308,7 @@
         <v>0</v>
       </c>
       <c r="E496" t="n">
-        <v>0.06467435508966446</v>
+        <v>0.1151322051882744</v>
       </c>
       <c r="F496" t="n">
         <v>3.90965092402464</v>
@@ -15338,7 +15338,7 @@
         <v>0</v>
       </c>
       <c r="E497" t="n">
-        <v>0.6640902757644653</v>
+        <v>0.6505488753318787</v>
       </c>
       <c r="F497" t="n">
         <v>7.3264887063655</v>
@@ -15368,7 +15368,7 @@
         <v>0</v>
       </c>
       <c r="E498" t="n">
-        <v>0.08781472593545914</v>
+        <v>0.0734211653470993</v>
       </c>
       <c r="F498" t="n">
         <v>4.13963039014374</v>
@@ -15398,7 +15398,7 @@
         <v>1</v>
       </c>
       <c r="E499" t="n">
-        <v>0.7876450419425964</v>
+        <v>0.6746776700019836</v>
       </c>
       <c r="F499" t="n">
         <v>22.1108829568789</v>
@@ -15428,7 +15428,7 @@
         <v>0</v>
       </c>
       <c r="E500" t="n">
-        <v>0.6686093807220459</v>
+        <v>0.5224360227584839</v>
       </c>
       <c r="F500" t="n">
         <v>15.3757700205339</v>
@@ -15458,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="E501" t="n">
-        <v>0.2403456121683121</v>
+        <v>0.1594677120447159</v>
       </c>
       <c r="F501" t="n">
         <v>5.48665297741273</v>
@@ -15488,7 +15488,7 @@
         <v>0</v>
       </c>
       <c r="E502" t="n">
-        <v>0.1311392933130264</v>
+        <v>0.1247337758541107</v>
       </c>
       <c r="F502" t="n">
         <v>3.1211498973306</v>
@@ -15518,7 +15518,7 @@
         <v>0</v>
       </c>
       <c r="E503" t="n">
-        <v>0.128962516784668</v>
+        <v>0.139555811882019</v>
       </c>
       <c r="F503" t="n">
         <v>20.6981519507187</v>
@@ -15548,7 +15548,7 @@
         <v>0</v>
       </c>
       <c r="E504" t="n">
-        <v>0.6314014792442322</v>
+        <v>0.5229348540306091</v>
       </c>
       <c r="F504" t="n">
         <v>6.40657084188912</v>
@@ -15578,7 +15578,7 @@
         <v>1</v>
       </c>
       <c r="E505" t="n">
-        <v>0.3632757961750031</v>
+        <v>0.8184300065040588</v>
       </c>
       <c r="F505" t="n">
         <v>13.21643836</v>
@@ -15608,7 +15608,7 @@
         <v>0</v>
       </c>
       <c r="E506" t="n">
-        <v>0.3288240134716034</v>
+        <v>0.4555832147598267</v>
       </c>
       <c r="F506" t="n">
         <v>56.71232877</v>
@@ -15638,7 +15638,7 @@
         <v>0</v>
       </c>
       <c r="E507" t="n">
-        <v>0.7038791179656982</v>
+        <v>0.8315277099609375</v>
       </c>
       <c r="F507" t="n">
         <v>63.50718686</v>
@@ -15668,7 +15668,7 @@
         <v>0</v>
       </c>
       <c r="E508" t="n">
-        <v>0.6451382040977478</v>
+        <v>0.5553593635559082</v>
       </c>
       <c r="F508" t="n">
         <v>27.00616016</v>
@@ -15698,7 +15698,7 @@
         <v>0</v>
       </c>
       <c r="E509" t="n">
-        <v>0.4647729396820068</v>
+        <v>0.4727675020694733</v>
       </c>
       <c r="F509" t="n">
         <v>13.43737166</v>
@@ -15728,7 +15728,7 @@
         <v>0</v>
       </c>
       <c r="E510" t="n">
-        <v>0.3946511149406433</v>
+        <v>0.3844153881072998</v>
       </c>
       <c r="F510" t="n">
         <v>8.049281314</v>
@@ -15758,7 +15758,7 @@
         <v>1</v>
       </c>
       <c r="E511" t="n">
-        <v>0.7151256203651428</v>
+        <v>0.8416517376899719</v>
       </c>
       <c r="F511" t="n">
         <v>42.28336756</v>
@@ -15788,7 +15788,7 @@
         <v>0</v>
       </c>
       <c r="E512" t="n">
-        <v>0.2403944283723831</v>
+        <v>0.2340914756059647</v>
       </c>
       <c r="F512" t="n">
         <v>15.11293635</v>
@@ -15818,7 +15818,7 @@
         <v>1</v>
       </c>
       <c r="E513" t="n">
-        <v>0.345890074968338</v>
+        <v>0.4005386233329773</v>
       </c>
       <c r="F513" t="n">
         <v>23.95071869</v>
@@ -15848,7 +15848,7 @@
         <v>1</v>
       </c>
       <c r="E514" t="n">
-        <v>0.7580809593200684</v>
+        <v>0.8758581876754761</v>
       </c>
       <c r="F514" t="n">
         <v>49.08418891</v>
@@ -15878,7 +15878,7 @@
         <v>1</v>
       </c>
       <c r="E515" t="n">
-        <v>0.5716089606285095</v>
+        <v>0.5222082138061523</v>
       </c>
       <c r="F515" t="n">
         <v>22.43942505</v>
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="E516" t="n">
-        <v>0.7584322690963745</v>
+        <v>0.9242458939552307</v>
       </c>
       <c r="F516" t="n">
         <v>3.58110883</v>
@@ -15938,7 +15938,7 @@
         <v>0</v>
       </c>
       <c r="E517" t="n">
-        <v>0.4229530990123749</v>
+        <v>0.3898065090179443</v>
       </c>
       <c r="F517" t="n">
         <v>10.64476386</v>
@@ -15968,7 +15968,7 @@
         <v>0</v>
       </c>
       <c r="E518" t="n">
-        <v>0.3002196848392487</v>
+        <v>0.2930454909801483</v>
       </c>
       <c r="F518" t="n">
         <v>56.54209446</v>
@@ -15998,7 +15998,7 @@
         <v>0</v>
       </c>
       <c r="E519" t="n">
-        <v>0.4668677151203156</v>
+        <v>0.3657298982143402</v>
       </c>
       <c r="F519" t="n">
         <v>3.811088296</v>
@@ -16028,7 +16028,7 @@
         <v>1</v>
       </c>
       <c r="E520" t="n">
-        <v>0.5361253619194031</v>
+        <v>0.5724556446075439</v>
       </c>
       <c r="F520" t="n">
         <v>13.17453799</v>
@@ -16058,7 +16058,7 @@
         <v>0</v>
       </c>
       <c r="E521" t="n">
-        <v>0.3496517241001129</v>
+        <v>0.3216719329357147</v>
       </c>
       <c r="F521" t="n">
         <v>2.924024641</v>
@@ -16088,7 +16088,7 @@
         <v>1</v>
       </c>
       <c r="E522" t="n">
-        <v>0.4389345347881317</v>
+        <v>0.4176663756370544</v>
       </c>
       <c r="F522" t="n">
         <v>36.96098563</v>
@@ -16118,7 +16118,7 @@
         <v>1</v>
       </c>
       <c r="E523" t="n">
-        <v>0.2854427993297577</v>
+        <v>0.3248823881149292</v>
       </c>
       <c r="F523" t="n">
         <v>55.49075975</v>
@@ -16148,7 +16148,7 @@
         <v>1</v>
       </c>
       <c r="E524" t="n">
-        <v>0.2724264860153198</v>
+        <v>0.498397022485733</v>
       </c>
       <c r="F524" t="n">
         <v>36.04106776</v>
@@ -16178,7 +16178,7 @@
         <v>0</v>
       </c>
       <c r="E525" t="n">
-        <v>0.6973093748092651</v>
+        <v>0.6248487234115601</v>
       </c>
       <c r="F525" t="n">
         <v>20.13963039</v>
@@ -16208,7 +16208,7 @@
         <v>1</v>
       </c>
       <c r="E526" t="n">
-        <v>0.9972182512283325</v>
+        <v>0.9999634027481079</v>
       </c>
       <c r="F526" t="n">
         <v>25.52772074</v>
@@ -16238,7 +16238,7 @@
         <v>1</v>
       </c>
       <c r="E527" t="n">
-        <v>0.7921091914176941</v>
+        <v>0.7876057028770447</v>
       </c>
       <c r="F527" t="n">
         <v>17.83983573</v>
@@ -16268,7 +16268,7 @@
         <v>0</v>
       </c>
       <c r="E528" t="n">
-        <v>0.3815637826919556</v>
+        <v>0.3278132975101471</v>
       </c>
       <c r="F528" t="n">
         <v>6.410958904</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="E529" t="n">
-        <v>0.5223584175109863</v>
+        <v>0.5242239832878113</v>
       </c>
       <c r="F529" t="n">
         <v>5.852054795</v>
@@ -16328,7 +16328,7 @@
         <v>0</v>
       </c>
       <c r="E530" t="n">
-        <v>0.2849128544330597</v>
+        <v>0.2726137042045593</v>
       </c>
       <c r="F530" t="n">
         <v>16.40547945</v>
@@ -16358,7 +16358,7 @@
         <v>1</v>
       </c>
       <c r="E531" t="n">
-        <v>0.5080738067626953</v>
+        <v>0.5051159858703613</v>
       </c>
       <c r="F531" t="n">
         <v>22.48767123</v>
@@ -16388,7 +16388,7 @@
         <v>1</v>
       </c>
       <c r="E532" t="n">
-        <v>0.7820369601249695</v>
+        <v>0.8361179828643799</v>
       </c>
       <c r="F532" t="n">
         <v>30.81724846</v>
@@ -16418,7 +16418,7 @@
         <v>0</v>
       </c>
       <c r="E533" t="n">
-        <v>0.2389563620090485</v>
+        <v>0.0563974566757679</v>
       </c>
       <c r="F533" t="n">
         <v>5.256673511</v>
@@ -16448,7 +16448,7 @@
         <v>0</v>
       </c>
       <c r="E534" t="n">
-        <v>0.3049474656581879</v>
+        <v>0.5247749090194702</v>
       </c>
       <c r="F534" t="n">
         <v>9.691991786000001</v>
@@ -16478,7 +16478,7 @@
         <v>1</v>
       </c>
       <c r="E535" t="n">
-        <v>0.890168309211731</v>
+        <v>0.912038266658783</v>
       </c>
       <c r="F535" t="n">
         <v>32.13141684</v>
@@ -16508,7 +16508,7 @@
         <v>0</v>
       </c>
       <c r="E536" t="n">
-        <v>0.7223037481307983</v>
+        <v>0.6989870071411133</v>
       </c>
       <c r="F536" t="n">
         <v>6.308008214</v>
@@ -16538,7 +16538,7 @@
         <v>1</v>
       </c>
       <c r="E537" t="n">
-        <v>0.8679100275039673</v>
+        <v>0.954477846622467</v>
       </c>
       <c r="F537" t="n">
         <v>24.27926078</v>
@@ -16568,7 +16568,7 @@
         <v>1</v>
       </c>
       <c r="E538" t="n">
-        <v>0.7951961755752563</v>
+        <v>0.7542880773544312</v>
       </c>
       <c r="F538" t="n">
         <v>20.63244353</v>
@@ -16598,7 +16598,7 @@
         <v>1</v>
       </c>
       <c r="E539" t="n">
-        <v>0.75260990858078</v>
+        <v>0.933941662311554</v>
       </c>
       <c r="F539" t="n">
         <v>25.36344969</v>
@@ -16628,7 +16628,7 @@
         <v>0</v>
       </c>
       <c r="E540" t="n">
-        <v>0.6748803853988647</v>
+        <v>0.7504151463508606</v>
       </c>
       <c r="F540" t="n">
         <v>20.69815195</v>
@@ -16658,7 +16658,7 @@
         <v>1</v>
       </c>
       <c r="E541" t="n">
-        <v>0.4676110744476318</v>
+        <v>0.2449642568826675</v>
       </c>
       <c r="F541" t="n">
         <v>20.10677618</v>
@@ -16688,7 +16688,7 @@
         <v>1</v>
       </c>
       <c r="E542" t="n">
-        <v>0.144549697637558</v>
+        <v>0.04240677505731583</v>
       </c>
       <c r="F542" t="n">
         <v>9.462012319999999</v>
@@ -16718,7 +16718,7 @@
         <v>0</v>
       </c>
       <c r="E543" t="n">
-        <v>0.4503496885299683</v>
+        <v>0.1765628457069397</v>
       </c>
       <c r="F543" t="n">
         <v>2.464065708</v>
@@ -16748,7 +16748,7 @@
         <v>1</v>
       </c>
       <c r="E544" t="n">
-        <v>0.6888637542724609</v>
+        <v>0.6088722944259644</v>
       </c>
       <c r="F544" t="n">
         <v>11.40041068</v>
@@ -16778,7 +16778,7 @@
         <v>1</v>
       </c>
       <c r="E545" t="n">
-        <v>0.4628291428089142</v>
+        <v>0.2543354034423828</v>
       </c>
       <c r="F545" t="n">
         <v>21.45379877</v>
@@ -16808,7 +16808,7 @@
         <v>0</v>
       </c>
       <c r="E546" t="n">
-        <v>0.5682581067085266</v>
+        <v>0.5494361519813538</v>
       </c>
       <c r="F546" t="n">
         <v>18.7926078</v>
@@ -16838,7 +16838,7 @@
         <v>0</v>
       </c>
       <c r="E547" t="n">
-        <v>0.09045424312353134</v>
+        <v>0.003977123182266951</v>
       </c>
       <c r="F547" t="n">
         <v>2.431211499</v>
@@ -16868,7 +16868,7 @@
         <v>0</v>
       </c>
       <c r="E548" t="n">
-        <v>0.5228613615036011</v>
+        <v>0.005830362439155579</v>
       </c>
       <c r="F548" t="n">
         <v>2.661190965</v>
@@ -16898,7 +16898,7 @@
         <v>0</v>
       </c>
       <c r="E549" t="n">
-        <v>0.7752754092216492</v>
+        <v>0.8189504146575928</v>
       </c>
       <c r="F549" t="n">
         <v>7.950718686</v>
@@ -16928,7 +16928,7 @@
         <v>0</v>
       </c>
       <c r="E550" t="n">
-        <v>0.7130754590034485</v>
+        <v>0.6867477297782898</v>
       </c>
       <c r="F550" t="n">
         <v>9.034907598</v>
@@ -16958,7 +16958,7 @@
         <v>0</v>
       </c>
       <c r="E551" t="n">
-        <v>0.363394021987915</v>
+        <v>0.6284692287445068</v>
       </c>
       <c r="F551" t="n">
         <v>11.69609856</v>
@@ -16988,7 +16988,7 @@
         <v>1</v>
       </c>
       <c r="E552" t="n">
-        <v>0.3799965977668762</v>
+        <v>0.3333185315132141</v>
       </c>
       <c r="F552" t="n">
         <v>33.01848049</v>
@@ -17018,7 +17018,7 @@
         <v>0</v>
       </c>
       <c r="E553" t="n">
-        <v>0.4472007751464844</v>
+        <v>0.005316369235515594</v>
       </c>
       <c r="F553" t="n">
         <v>4.303901437</v>
@@ -17048,7 +17048,7 @@
         <v>0</v>
       </c>
       <c r="E554" t="n">
-        <v>0.2354910373687744</v>
+        <v>0.01725182123482227</v>
       </c>
       <c r="F554" t="n">
         <v>2.332648871</v>
@@ -17078,7 +17078,7 @@
         <v>1</v>
       </c>
       <c r="E555" t="n">
-        <v>0.7635294795036316</v>
+        <v>0.9302787184715271</v>
       </c>
       <c r="F555" t="n">
         <v>30.2587269</v>
@@ -17108,7 +17108,7 @@
         <v>0</v>
       </c>
       <c r="E556" t="n">
-        <v>0.3331395089626312</v>
+        <v>0.2784120142459869</v>
       </c>
       <c r="F556" t="n">
         <v>5.289093298291721</v>
@@ -17138,7 +17138,7 @@
         <v>1</v>
       </c>
       <c r="E557" t="n">
-        <v>0.7065561413764954</v>
+        <v>0.6969504952430725</v>
       </c>
       <c r="F557" t="n">
         <v>9.756898817345595</v>
@@ -17168,7 +17168,7 @@
         <v>1</v>
       </c>
       <c r="E558" t="n">
-        <v>0.4753513634204865</v>
+        <v>0.7571691274642944</v>
       </c>
       <c r="F558" t="n">
         <v>20.89356110381077</v>
@@ -17228,7 +17228,7 @@
         <v>0</v>
       </c>
       <c r="E560" t="n">
-        <v>0.9087767004966736</v>
+        <v>0.9886753559112549</v>
       </c>
       <c r="F560" t="n">
         <v>1.051248357424442</v>
@@ -17258,7 +17258,7 @@
         <v>1</v>
       </c>
       <c r="E561" t="n">
-        <v>0.4501722157001495</v>
+        <v>0.6211987137794495</v>
       </c>
       <c r="F561" t="n">
         <v>38.17345597897503</v>
@@ -17288,7 +17288,7 @@
         <v>1</v>
       </c>
       <c r="E562" t="n">
-        <v>0.6973228454589844</v>
+        <v>0.5301117300987244</v>
       </c>
       <c r="F562" t="n">
         <v>3.942181340341656</v>
@@ -17318,7 +17318,7 @@
         <v>0</v>
       </c>
       <c r="E563" t="n">
-        <v>0.4441528916358948</v>
+        <v>0.4958815574645996</v>
       </c>
       <c r="F563" t="n">
         <v>3.909329829172142</v>
@@ -17348,7 +17348,7 @@
         <v>0</v>
       </c>
       <c r="E564" t="n">
-        <v>0.323737770318985</v>
+        <v>0.2520941197872162</v>
       </c>
       <c r="F564" t="n">
         <v>9.888304862023652</v>
@@ -17378,7 +17378,7 @@
         <v>0</v>
       </c>
       <c r="E565" t="n">
-        <v>0.9999977350234985</v>
+        <v>1</v>
       </c>
       <c r="F565" t="n">
         <v>4.073587385019711</v>
@@ -17408,7 +17408,7 @@
         <v>0</v>
       </c>
       <c r="E566" t="n">
-        <v>0.937418520450592</v>
+        <v>0.9461908340454102</v>
       </c>
       <c r="F566" t="n">
         <v>4.533508541392904</v>
@@ -17438,7 +17438,7 @@
         <v>1</v>
       </c>
       <c r="E567" t="n">
-        <v>0.4578899443149567</v>
+        <v>0.5398701429367065</v>
       </c>
       <c r="F567" t="n">
         <v>11.85939553219448</v>
@@ -17468,7 +17468,7 @@
         <v>1</v>
       </c>
       <c r="E568" t="n">
-        <v>0.9932472705841064</v>
+        <v>0.9974120259284973</v>
       </c>
       <c r="F568" t="n">
         <v>14.25755584756899</v>
@@ -17498,7 +17498,7 @@
         <v>1</v>
       </c>
       <c r="E569" t="n">
-        <v>0.9600430130958557</v>
+        <v>0.9649467468261719</v>
       </c>
       <c r="F569" t="n">
         <v>19.54664914586071</v>
@@ -17528,7 +17528,7 @@
         <v>0</v>
       </c>
       <c r="E570" t="n">
-        <v>0.4343695938587189</v>
+        <v>0.4610716104507446</v>
       </c>
       <c r="F570" t="n">
         <v>3.416557161629435</v>
@@ -17558,7 +17558,7 @@
         <v>0</v>
       </c>
       <c r="E571" t="n">
-        <v>0.9349831342697144</v>
+        <v>0.9037416577339172</v>
       </c>
       <c r="F571" t="n">
         <v>2.49691991786448</v>
@@ -17588,7 +17588,7 @@
         <v>1</v>
       </c>
       <c r="E572" t="n">
-        <v>0.2350233346223831</v>
+        <v>0.3073790669441223</v>
       </c>
       <c r="F572" t="n">
         <v>23.2607802874743</v>
@@ -17618,7 +17618,7 @@
         <v>0</v>
       </c>
       <c r="E573" t="n">
-        <v>0.03817351162433624</v>
+        <v>0.08280597627162933</v>
       </c>
       <c r="F573" t="n">
         <v>2.23408624229979</v>
@@ -17648,7 +17648,7 @@
         <v>0</v>
       </c>
       <c r="E574" t="n">
-        <v>0.8715458512306213</v>
+        <v>0.851850688457489</v>
       </c>
       <c r="F574" t="n">
         <v>10.4147843942505</v>
@@ -17678,7 +17678,7 @@
         <v>0</v>
       </c>
       <c r="E575" t="n">
-        <v>0.1463668644428253</v>
+        <v>0.1384147703647614</v>
       </c>
       <c r="F575" t="n">
         <v>1.47843942505133</v>
@@ -17708,7 +17708,7 @@
         <v>0</v>
       </c>
       <c r="E576" t="n">
-        <v>0.06754323840141296</v>
+        <v>0.06010143458843231</v>
       </c>
       <c r="F576" t="n">
         <v>10.8747433264887</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="E577" t="n">
-        <v>0.699625551700592</v>
+        <v>0.8291008472442627</v>
       </c>
       <c r="F577" t="n">
         <v>16.4599589322382</v>
@@ -17768,7 +17768,7 @@
         <v>0</v>
       </c>
       <c r="E578" t="n">
-        <v>0.492030143737793</v>
+        <v>0.2637381553649902</v>
       </c>
       <c r="F578" t="n">
         <v>15.8685831622177</v>
@@ -17798,7 +17798,7 @@
         <v>0</v>
       </c>
       <c r="E579" t="n">
-        <v>0.4114562273025513</v>
+        <v>0.4244123101234436</v>
       </c>
       <c r="F579" t="n">
         <v>2.10266940451745</v>
@@ -17828,7 +17828,7 @@
         <v>0</v>
       </c>
       <c r="E580" t="n">
-        <v>0.5502054691314697</v>
+        <v>0.3608213067054749</v>
       </c>
       <c r="F580" t="n">
         <v>20.7638603696099</v>
@@ -17858,7 +17858,7 @@
         <v>0</v>
       </c>
       <c r="E581" t="n">
-        <v>0.7144145965576172</v>
+        <v>0.641240656375885</v>
       </c>
       <c r="F581" t="n">
         <v>2.23408624229979</v>
@@ -17888,7 +17888,7 @@
         <v>1</v>
       </c>
       <c r="E582" t="n">
-        <v>0.2696891129016876</v>
+        <v>0.500485897064209</v>
       </c>
       <c r="F582" t="n">
         <v>22.1437371663244</v>
@@ -17918,7 +17918,7 @@
         <v>0</v>
       </c>
       <c r="E583" t="n">
-        <v>0.09899916499853134</v>
+        <v>0.3397108614444733</v>
       </c>
       <c r="F583" t="n">
         <v>18.1683778234086</v>
@@ -17948,7 +17948,7 @@
         <v>1</v>
       </c>
       <c r="E584" t="n">
-        <v>0.9091533422470093</v>
+        <v>0.8832635879516602</v>
       </c>
       <c r="F584" t="n">
         <v>21.4537987679671</v>
@@ -17978,7 +17978,7 @@
         <v>0</v>
       </c>
       <c r="E585" t="n">
-        <v>0.7810664772987366</v>
+        <v>0.7959267497062683</v>
       </c>
       <c r="F585" t="n">
         <v>6.96509240246407</v>
@@ -18008,7 +18008,7 @@
         <v>0</v>
       </c>
       <c r="E586" t="n">
-        <v>0.3160030543804169</v>
+        <v>0.1815194934606552</v>
       </c>
       <c r="F586" t="n">
         <v>1.41273100616016</v>
@@ -18038,7 +18038,7 @@
         <v>0</v>
       </c>
       <c r="E587" t="n">
-        <v>0.1561615020036697</v>
+        <v>0.1088286340236664</v>
       </c>
       <c r="F587" t="n">
         <v>3.48254620123203</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="E588" t="n">
-        <v>0.4320395588874817</v>
+        <v>0.347212165594101</v>
       </c>
       <c r="F588" t="n">
         <v>3.87679671457906</v>
@@ -18098,7 +18098,7 @@
         <v>0</v>
       </c>
       <c r="E589" t="n">
-        <v>0.2891123592853546</v>
+        <v>0.1430647224187851</v>
       </c>
       <c r="F589" t="n">
         <v>5.88090349075975</v>
@@ -18128,7 +18128,7 @@
         <v>0</v>
       </c>
       <c r="E590" t="n">
-        <v>0.05051824077963829</v>
+        <v>0.08172565698623657</v>
       </c>
       <c r="F590" t="n">
         <v>7.95071868583162</v>
@@ -18158,7 +18158,7 @@
         <v>0</v>
       </c>
       <c r="E591" t="n">
-        <v>0.05990678444504738</v>
+        <v>0.08564714342355728</v>
       </c>
       <c r="F591" t="n">
         <v>6.70225872689938</v>
@@ -18188,7 +18188,7 @@
         <v>1</v>
       </c>
       <c r="E592" t="n">
-        <v>0.1241558641195297</v>
+        <v>0.3212608098983765</v>
       </c>
       <c r="F592" t="n">
         <v>18.1683778234086</v>
@@ -18218,7 +18218,7 @@
         <v>0</v>
       </c>
       <c r="E593" t="n">
-        <v>0.1190144643187523</v>
+        <v>0.05244411528110504</v>
       </c>
       <c r="F593" t="n">
         <v>5.68377823408624</v>
@@ -18248,7 +18248,7 @@
         <v>0</v>
       </c>
       <c r="E594" t="n">
-        <v>0.5379230976104736</v>
+        <v>0.6439056992530823</v>
       </c>
       <c r="F594" t="n">
         <v>3.44969199178645</v>
@@ -18278,7 +18278,7 @@
         <v>0</v>
       </c>
       <c r="E595" t="n">
-        <v>0.9705378413200378</v>
+        <v>0.9408171772956848</v>
       </c>
       <c r="F595" t="n">
         <v>21.388090349076</v>
@@ -18308,7 +18308,7 @@
         <v>0</v>
       </c>
       <c r="E596" t="n">
-        <v>0.7165234088897705</v>
+        <v>0.7255587577819824</v>
       </c>
       <c r="F596" t="n">
         <v>6.24229979466119</v>
@@ -18338,7 +18338,7 @@
         <v>1</v>
       </c>
       <c r="E597" t="n">
-        <v>0.4190895557403564</v>
+        <v>0.7847015857696533</v>
       </c>
       <c r="F597" t="n">
         <v>19.2854209445585</v>
@@ -18368,7 +18368,7 @@
         <v>1</v>
       </c>
       <c r="E598" t="n">
-        <v>0.4346637427806854</v>
+        <v>0.7649921774864197</v>
       </c>
       <c r="F598" t="n">
         <v>18.7268993839836</v>
@@ -18398,7 +18398,7 @@
         <v>0</v>
       </c>
       <c r="E599" t="n">
-        <v>0.6931421160697937</v>
+        <v>0.6582752466201782</v>
       </c>
       <c r="F599" t="n">
         <v>19.1211498973306</v>
@@ -18428,7 +18428,7 @@
         <v>1</v>
       </c>
       <c r="E600" t="n">
-        <v>0.2547835111618042</v>
+        <v>0.1392848491668701</v>
       </c>
       <c r="F600" t="n">
         <v>19.4168377823409</v>
@@ -18458,7 +18458,7 @@
         <v>0</v>
       </c>
       <c r="E601" t="n">
-        <v>0.1260223835706711</v>
+        <v>0.04110592231154442</v>
       </c>
       <c r="F601" t="n">
         <v>1.67556468172485</v>
@@ -18488,7 +18488,7 @@
         <v>0</v>
       </c>
       <c r="E602" t="n">
-        <v>0.3568045794963837</v>
+        <v>0.3844259679317474</v>
       </c>
       <c r="F602" t="n">
         <v>20.7310061601643</v>
@@ -18518,7 +18518,7 @@
         <v>0</v>
       </c>
       <c r="E603" t="n">
-        <v>0.4627580046653748</v>
+        <v>0.2461728304624557</v>
       </c>
       <c r="F603" t="n">
         <v>2.23408624229979</v>
@@ -18548,7 +18548,7 @@
         <v>0</v>
       </c>
       <c r="E604" t="n">
-        <v>0.631548285484314</v>
+        <v>0.3485141396522522</v>
       </c>
       <c r="F604" t="n">
         <v>8.83778234086242</v>
@@ -18578,7 +18578,7 @@
         <v>0</v>
       </c>
       <c r="E605" t="n">
-        <v>0.4971076548099518</v>
+        <v>0.3537076413631439</v>
       </c>
       <c r="F605" t="n">
         <v>19.1211498973306</v>
@@ -18608,7 +18608,7 @@
         <v>0</v>
       </c>
       <c r="E606" t="n">
-        <v>0.7760127186775208</v>
+        <v>0.7876879572868347</v>
       </c>
       <c r="F606" t="n">
         <v>1.74127310061602</v>
@@ -18638,7 +18638,7 @@
         <v>0</v>
       </c>
       <c r="E607" t="n">
-        <v>0.7890771627426147</v>
+        <v>0.8057404160499573</v>
       </c>
       <c r="F607" t="n">
         <v>5.12525667351129</v>
@@ -18668,7 +18668,7 @@
         <v>0</v>
       </c>
       <c r="E608" t="n">
-        <v>0.1987335979938507</v>
+        <v>0.3626468777656555</v>
       </c>
       <c r="F608" t="n">
         <v>21.8480492813142</v>
@@ -18698,7 +18698,7 @@
         <v>0</v>
       </c>
       <c r="E609" t="n">
-        <v>0.1708234846591949</v>
+        <v>0.09157288074493408</v>
       </c>
       <c r="F609" t="n">
         <v>13.305954825462</v>
@@ -18728,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="E610" t="n">
-        <v>0.1091322675347328</v>
+        <v>0.264947235584259</v>
       </c>
       <c r="F610" t="n">
         <v>21.1581108829569</v>
@@ -18758,7 +18758,7 @@
         <v>1</v>
       </c>
       <c r="E611" t="n">
-        <v>0.4654935896396637</v>
+        <v>0.5597770810127258</v>
       </c>
       <c r="F611" t="n">
         <v>20.8624229979466</v>
@@ -18788,7 +18788,7 @@
         <v>0</v>
       </c>
       <c r="E612" t="n">
-        <v>0.03497428074479103</v>
+        <v>0.1263006031513214</v>
       </c>
       <c r="F612" t="n">
         <v>4.36960985626283</v>
@@ -18818,7 +18818,7 @@
         <v>0</v>
       </c>
       <c r="E613" t="n">
-        <v>0.572032630443573</v>
+        <v>0.425304114818573</v>
       </c>
       <c r="F613" t="n">
         <v>21.0266940451745</v>
@@ -18848,7 +18848,7 @@
         <v>0</v>
       </c>
       <c r="E614" t="n">
-        <v>0.7879164218902588</v>
+        <v>0.8363295793533325</v>
       </c>
       <c r="F614" t="n">
         <v>13.4045174537988</v>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="E615" t="n">
-        <v>0.6715583205223083</v>
+        <v>0.7676430940628052</v>
       </c>
       <c r="F615" t="n">
         <v>20.6324435318275</v>
@@ -18908,7 +18908,7 @@
         <v>0</v>
       </c>
       <c r="E616" t="n">
-        <v>0.05546500533819199</v>
+        <v>0.034775760024786</v>
       </c>
       <c r="F616" t="n">
         <v>6.70225872689938</v>
@@ -18938,7 +18938,7 @@
         <v>0</v>
       </c>
       <c r="E617" t="n">
-        <v>0.1103959456086159</v>
+        <v>0.04860356077551842</v>
       </c>
       <c r="F617" t="n">
         <v>13.2731006160164</v>
@@ -18968,7 +18968,7 @@
         <v>0</v>
       </c>
       <c r="E618" t="n">
-        <v>0.6078141331672668</v>
+        <v>0.5087897181510925</v>
       </c>
       <c r="F618" t="n">
         <v>9.5605749486653</v>
@@ -18998,7 +18998,7 @@
         <v>1</v>
       </c>
       <c r="E619" t="n">
-        <v>0.5074409246444702</v>
+        <v>0.5829360485076904</v>
       </c>
       <c r="F619" t="n">
         <v>20.7310061601643</v>
@@ -19028,7 +19028,7 @@
         <v>1</v>
       </c>
       <c r="E620" t="n">
-        <v>0.3836624026298523</v>
+        <v>0.1476584821939468</v>
       </c>
       <c r="F620" t="n">
         <v>23.523613963039</v>
@@ -19058,7 +19058,7 @@
         <v>1</v>
       </c>
       <c r="E621" t="n">
-        <v>0.8767691254615784</v>
+        <v>0.8671720623970032</v>
       </c>
       <c r="F621" t="n">
         <v>20.829568788501</v>
@@ -19088,7 +19088,7 @@
         <v>0</v>
       </c>
       <c r="E622" t="n">
-        <v>0.1185090988874435</v>
+        <v>0.0813586488366127</v>
       </c>
       <c r="F622" t="n">
         <v>10.4804928131417</v>
@@ -19118,7 +19118,7 @@
         <v>1</v>
       </c>
       <c r="E623" t="n">
-        <v>0.2321288734674454</v>
+        <v>0.2877688407897949</v>
       </c>
       <c r="F623" t="n">
         <v>20.2710472279261</v>
@@ -19148,7 +19148,7 @@
         <v>0</v>
       </c>
       <c r="E624" t="n">
-        <v>0.1896168291568756</v>
+        <v>0.06579115986824036</v>
       </c>
       <c r="F624" t="n">
         <v>6.11088295687885</v>
@@ -19178,7 +19178,7 @@
         <v>0</v>
       </c>
       <c r="E625" t="n">
-        <v>0.12786565721035</v>
+        <v>0.04859922453761101</v>
       </c>
       <c r="F625" t="n">
         <v>1.97125256673511</v>
@@ -19208,7 +19208,7 @@
         <v>0</v>
       </c>
       <c r="E626" t="n">
-        <v>0.4073582291603088</v>
+        <v>0.3832016587257385</v>
       </c>
       <c r="F626" t="n">
         <v>8.08213552361396</v>
@@ -19238,7 +19238,7 @@
         <v>0</v>
       </c>
       <c r="E627" t="n">
-        <v>0.722643256187439</v>
+        <v>0.7451526522636414</v>
       </c>
       <c r="F627" t="n">
         <v>4.36960985626283</v>
@@ -19268,7 +19268,7 @@
         <v>1</v>
       </c>
       <c r="E628" t="n">
-        <v>0.9243982434272766</v>
+        <v>0.8924508690834045</v>
       </c>
       <c r="F628" t="n">
         <v>22.5379876796715</v>
@@ -19298,7 +19298,7 @@
         <v>0</v>
       </c>
       <c r="E629" t="n">
-        <v>0.4413976073265076</v>
+        <v>0.3011715710163116</v>
       </c>
       <c r="F629" t="n">
         <v>9.034907597535931</v>
